--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.0%</t>
+          <t>-668.1%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.7%</t>
+          <t>-127.8%</t>
         </is>
       </c>
     </row>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710419</v>
+        <v>3.705221264710418</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893117</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71556459695019</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171926</v>
+        <v>3.673998560171925</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692302</v>
+        <v>3.682496284692301</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
@@ -49339,16 +49339,16 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.715372213494433</v>
+        <v>3.715372213494432</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.064641856464092</v>
+        <v>-5.065115083888786</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.484833497026979</v>
+        <v>2.484644206057101</v>
       </c>
       <c r="F2078" t="n">
         <v>0.7180210854131662</v>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>423.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.1%</t>
+          <t>-654.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.8%</t>
+          <t>-122.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.1%</t>
+          <t>588.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-307.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-144.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.002282108192627</v>
+        <v>-4.859316643025358</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.199128253636283</v>
+        <v>2.25631443970319</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7419520194292824</v>
+        <v>0.8144834768704026</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.645568732884651</v>
+        <v>4.689087607349323</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.011118905608746</v>
+        <v>-4.868153440441477</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.178012736490337</v>
+        <v>2.235198922557244</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7345098467879316</v>
+        <v>0.8070413042290518</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.623522631120342</v>
+        <v>4.667041505585014</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.102501468174204</v>
+        <v>-4.959536003006936</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.151624222509203</v>
+        <v>2.20881040857611</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6431272842224733</v>
+        <v>0.7156587416635936</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.578857604626116</v>
+        <v>4.622376479090788</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.090794750187198</v>
+        <v>-4.94782928501993</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.258435167528273</v>
+        <v>2.315621353595181</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6548340022094797</v>
+        <v>0.7273654596506</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.688009893242588</v>
+        <v>4.73152876770726</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.991131246103536</v>
+        <v>-4.848165780936267</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.301332907893143</v>
+        <v>2.358519093960051</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.7905525428542864</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.728954481896205</v>
+        <v>4.772473356360877</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.715372213494432</v>
+        <v>3.813633677223936</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.065115083888786</v>
+        <v>-4.928386370129308</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.484644206057101</v>
+        <v>2.539335691560892</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.7905525428542864</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.941859315174263</v>
+        <v>4.985378189638936</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.2%</t>
+          <t>423.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.4%</t>
+          <t>-662.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-122.3%</t>
+          <t>-125.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.6%</t>
+          <t>-307.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-144.9%</t>
+          <t>-146.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.279940464198855</v>
+        <v>-4.222242229956125</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.028065241780731</v>
+        <v>2.051144535477824</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9313233081456711</v>
+        <v>0.9890215423884019</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.299191836661424</v>
+        <v>4.333810777207062</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.321095583767076</v>
+        <v>-4.263397349524346</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.013483824137579</v>
+        <v>2.036563117834671</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8901681885774502</v>
+        <v>0.947866422820181</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.276379395104627</v>
+        <v>4.310998335650265</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.253047021075546</v>
+        <v>-4.195348786832816</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.053554275092074</v>
+        <v>2.076633568789165</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.95821675126898</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.330059558597427</v>
+        <v>4.364678499143066</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.484647414245047</v>
+        <v>-4.426949180002317</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.981116787997867</v>
+        <v>2.00419608169496</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.95821675126898</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.350262228771022</v>
+        <v>4.38488116931666</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.502719922536659</v>
+        <v>-4.445021688293928</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.973887784681223</v>
+        <v>1.996967078378315</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.95821675126898</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.350262228771022</v>
+        <v>4.38488116931666</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.677826755113104</v>
+        <v>-4.620128520870374</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.864096965244111</v>
+        <v>1.887176258941203</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.95821675126898</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.310514142364489</v>
+        <v>4.345133082910126</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.646540734572649</v>
+        <v>-4.588842500329918</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.883633992457233</v>
+        <v>1.906713286154325</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9895027718094354</v>
+        <v>1.047201006052166</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.336308373685702</v>
+        <v>4.37092731423134</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.493515342459364</v>
+        <v>-4.435817108216634</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.044015148875451</v>
+        <v>2.067094442572543</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.142528163922719</v>
+        <v>1.20022639816545</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.527294608526576</v>
+        <v>4.561913549072215</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.521822656332635</v>
+        <v>-4.464124422089904</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.220158448234435</v>
+        <v>2.243237741931527</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.142528163922719</v>
+        <v>1.20022639816545</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.714760833434869</v>
+        <v>4.749379773980507</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.688415881446157</v>
+        <v>-4.630717647203427</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.122924109543109</v>
+        <v>2.146003403240201</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9759349388091969</v>
+        <v>1.033633173051928</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.584207849720837</v>
+        <v>4.618826790266476</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.665380088084591</v>
+        <v>-4.607681853841861</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.135814829549453</v>
+        <v>2.158894123246545</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9759349388091969</v>
+        <v>1.033633173051928</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.587884252382555</v>
+        <v>4.622503192928193</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.636134107628894</v>
+        <v>-4.578435873386164</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.145131276855227</v>
+        <v>2.168210570552319</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9759349388091969</v>
+        <v>1.033633173051928</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.58550230750605</v>
+        <v>4.620121248051689</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.743059655506745</v>
+        <v>-4.685361421264015</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.099654296861721</v>
+        <v>2.122733590558814</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8690093909313455</v>
+        <v>0.9267076251740763</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.518640217936975</v>
+        <v>4.553259158482613</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.888078214013994</v>
+        <v>-4.830379979771264</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.043075675602056</v>
+        <v>2.066154969299149</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.723990832424097</v>
+        <v>0.7816890666668278</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.43305788497586</v>
+        <v>4.467676825521498</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.006419979798712</v>
+        <v>-4.948721745555981</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.095670208545922</v>
+        <v>2.118749502243015</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.539400747371347</v>
+        <v>4.574019687916985</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.05783040211942</v>
+        <v>-5.000132167876689</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.072891736743578</v>
+        <v>2.09597103044067</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.537186444497285</v>
+        <v>4.571805385042923</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.137249853327171</v>
+        <v>-5.079551619084441</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.041027084334766</v>
+        <v>2.064106378031858</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.537089572571575</v>
+        <v>4.571708513117214</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.232712851244389</v>
+        <v>-5.175014617001659</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.002835778725923</v>
+        <v>2.025915072423015</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.537083466129618</v>
+        <v>4.571702406675257</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.168336940393674</v>
+        <v>-5.110638706150944</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.02668253962882</v>
+        <v>2.049761833325912</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7990527818377022</v>
+        <v>0.856751016080433</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.573805409202658</v>
+        <v>4.608424349748296</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.223706102525868</v>
+        <v>-5.166007868283137</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.010268692523669</v>
+        <v>2.033347986220761</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7990527818377022</v>
+        <v>0.856751016080433</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.579539226950384</v>
+        <v>4.614158167496023</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396014</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.269143882356695</v>
+        <v>-5.211445648113965</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.991631943934271</v>
+        <v>2.014711237631363</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.553370595886422</v>
+        <v>4.58798953643206</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396423</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.180937048209117</v>
+        <v>-5.123238813966386</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.046789070443621</v>
+        <v>2.069868364140713</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.573244988736741</v>
+        <v>4.607863929282379</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.074902053003807</v>
+        <v>-5.017203818761077</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.072903769050473</v>
+        <v>2.095983062747565</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.556945689261469</v>
+        <v>4.591564629807107</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.891690389870712</v>
+        <v>-4.833992155627982</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.148619383767756</v>
+        <v>2.171698677464848</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.559376638725515</v>
+        <v>4.593995579271152</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.819968942856861</v>
+        <v>-4.762270708614131</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.143099148421186</v>
+        <v>2.166178442118278</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8279292381733933</v>
+        <v>0.8856274724161241</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.568200692781714</v>
+        <v>4.602819633327353</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.797595917249155</v>
+        <v>-4.739897683006425</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.09896410458544</v>
+        <v>2.122043398282532</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8391849892862948</v>
+        <v>0.8968832235290256</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.521869889370627</v>
+        <v>4.556488829916265</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.8306122131599</v>
+        <v>-4.77291397891717</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.270955791106497</v>
+        <v>2.29403508480359</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7697476126195433</v>
+        <v>0.8274458468622741</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.665405668255931</v>
+        <v>4.70002460880157</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.819084577510291</v>
+        <v>-4.761386343267561</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.26748807119459</v>
+        <v>2.290567364891682</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8287482708209057</v>
+        <v>0.8864465050636365</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.692727289004997</v>
+        <v>4.727346229550636</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.91642607885266</v>
+        <v>-4.85872784460993</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.232219583179432</v>
+        <v>2.255298876876523</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7843280886554174</v>
+        <v>0.8420263228981482</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.669743292227493</v>
+        <v>4.704362232773132</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.859316643025358</v>
+        <v>-4.944583873949896</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.25631443970319</v>
+        <v>2.222207547333375</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8144834768704026</v>
+        <v>0.7996502536720131</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.689087607349323</v>
+        <v>4.680187673430289</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.868153440441477</v>
+        <v>-4.953420671366016</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.235198922557244</v>
+        <v>2.201092030187429</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8070413042290518</v>
+        <v>0.7922080810306624</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.667041505585014</v>
+        <v>4.65814157166598</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.959536003006936</v>
+        <v>-5.044803233931474</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.20881040857611</v>
+        <v>2.174703516206295</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7156587416635936</v>
+        <v>0.7008255184652041</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.622376479090788</v>
+        <v>4.613476545171755</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171925</v>
+        <v>3.673998560171924</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.94782928501993</v>
+        <v>-5.033096515944468</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.315621353595181</v>
+        <v>2.281514461225365</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7273654596506</v>
+        <v>0.7125322364522105</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.73152876770726</v>
+        <v>4.722628833788226</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692301</v>
+        <v>3.6824962846923</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.848165780936267</v>
+        <v>-4.933433011860806</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.358519093960051</v>
+        <v>2.324412201590236</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.7905525428542864</v>
+        <v>0.775719319655897</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.772473356360877</v>
+        <v>4.763573422441843</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.813633677223936</v>
+        <v>3.758857323081443</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.928386370129308</v>
+        <v>-5.013653601053846</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.539335691560892</v>
+        <v>2.505228799191077</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.7905525428542864</v>
+        <v>0.775719319655897</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.985378189638936</v>
+        <v>4.976478255719901</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.5%</t>
+          <t>152.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.1%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.9%</t>
+          <t>-661.7%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.7%</t>
+          <t>-125.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.1%</t>
+          <t>589.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.8%</t>
+          <t>-308.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-146.4%</t>
+          <t>-152.2%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>104.6%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2078"/>
+  <dimension ref="A1:G2079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.222242229956125</v>
+        <v>-4.279940464198855</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.051144535477824</v>
+        <v>2.028065241780731</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9890215423884019</v>
+        <v>0.9313233081456711</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.333810777207062</v>
+        <v>4.299191836661424</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.263397349524346</v>
+        <v>-4.321095583767076</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.036563117834671</v>
+        <v>2.013483824137579</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.947866422820181</v>
+        <v>0.8901681885774502</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.310998335650265</v>
+        <v>4.276379395104627</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.195348786832816</v>
+        <v>-4.253047021075546</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.076633568789165</v>
+        <v>2.053554275092074</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.015914985511711</v>
+        <v>0.95821675126898</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.364678499143066</v>
+        <v>4.330059558597427</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760316</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.426949180002317</v>
+        <v>-4.484647414245047</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.00419608169496</v>
+        <v>1.981116787997867</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.015914985511711</v>
+        <v>0.95821675126898</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.38488116931666</v>
+        <v>4.350262228771022</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.445021688293928</v>
+        <v>-4.502719922536659</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.996967078378315</v>
+        <v>1.973887784681223</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.015914985511711</v>
+        <v>0.95821675126898</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.38488116931666</v>
+        <v>4.350262228771022</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.620128520870374</v>
+        <v>-4.677826755113104</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.887176258941203</v>
+        <v>1.864096965244111</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.015914985511711</v>
+        <v>0.95821675126898</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.345133082910126</v>
+        <v>4.310514142364489</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943588</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.588842500329918</v>
+        <v>-4.646540734572649</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.906713286154325</v>
+        <v>1.883633992457233</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.047201006052166</v>
+        <v>0.9895027718094354</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.37092731423134</v>
+        <v>4.336308373685702</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.435817108216634</v>
+        <v>-4.493515342459364</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.067094442572543</v>
+        <v>2.044015148875451</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.20022639816545</v>
+        <v>1.142528163922719</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.561913549072215</v>
+        <v>4.527294608526576</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073884</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.464124422089904</v>
+        <v>-4.521822656332635</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.243237741931527</v>
+        <v>2.220158448234435</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.20022639816545</v>
+        <v>1.142528163922719</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.749379773980507</v>
+        <v>4.714760833434869</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.630717647203427</v>
+        <v>-4.688415881446157</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.146003403240201</v>
+        <v>2.122924109543109</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.033633173051928</v>
+        <v>0.9759349388091969</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.618826790266476</v>
+        <v>4.584207849720837</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.607681853841861</v>
+        <v>-4.665380088084591</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.158894123246545</v>
+        <v>2.135814829549453</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.033633173051928</v>
+        <v>0.9759349388091969</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.622503192928193</v>
+        <v>4.587884252382555</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.578435873386164</v>
+        <v>-4.636134107628894</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.168210570552319</v>
+        <v>2.145131276855227</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.033633173051928</v>
+        <v>0.9759349388091969</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.620121248051689</v>
+        <v>4.58550230750605</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.685361421264015</v>
+        <v>-4.743059655506745</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.122733590558814</v>
+        <v>2.099654296861721</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9267076251740763</v>
+        <v>0.8690093909313455</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.553259158482613</v>
+        <v>4.518640217936975</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.830379979771264</v>
+        <v>-4.888078214013994</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.066154969299149</v>
+        <v>2.043075675602056</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7816890666668278</v>
+        <v>0.723990832424097</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.467676825521498</v>
+        <v>4.43305788497586</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.948721745555981</v>
+        <v>-5.006419979798712</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.118749502243015</v>
+        <v>2.095670208545922</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7346768709869871</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.574019687916985</v>
+        <v>4.539400747371347</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.000132167876689</v>
+        <v>-5.05783040211942</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.09597103044067</v>
+        <v>2.072891736743578</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7346768709869871</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.571805385042923</v>
+        <v>4.537186444497285</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.079551619084441</v>
+        <v>-5.137249853327171</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.064106378031858</v>
+        <v>2.041027084334766</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7346768709869871</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.571708513117214</v>
+        <v>4.537089572571575</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.175014617001659</v>
+        <v>-5.232712851244389</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.025915072423015</v>
+        <v>2.002835778725923</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7346768709869871</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.571702406675257</v>
+        <v>4.537083466129618</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.110638706150944</v>
+        <v>-5.168336940393674</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.049761833325912</v>
+        <v>2.02668253962882</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.856751016080433</v>
+        <v>0.7990527818377022</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.608424349748296</v>
+        <v>4.573805409202658</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.166007868283137</v>
+        <v>-5.223706102525868</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.033347986220761</v>
+        <v>2.010268692523669</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.856751016080433</v>
+        <v>0.7990527818377022</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.614158167496023</v>
+        <v>4.579539226950384</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396014</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.211445648113965</v>
+        <v>-5.269143882356695</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.014711237631363</v>
+        <v>1.991631943934271</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.7562077911595426</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.58798953643206</v>
+        <v>4.553370595886422</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396423</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.123238813966386</v>
+        <v>-5.180937048209117</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.069868364140713</v>
+        <v>2.046789070443621</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.7562077911595426</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.607863929282379</v>
+        <v>4.573244988736741</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299176</v>
+        <v>3.794507029299178</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.017203818761077</v>
+        <v>-5.074902053003807</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.095983062747565</v>
+        <v>2.072903769050473</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.7562077911595426</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.591564629807107</v>
+        <v>4.556945689261469</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590409</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.833992155627982</v>
+        <v>-4.891690389870712</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.171698677464848</v>
+        <v>2.148619383767756</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.7562077911595426</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.593995579271152</v>
+        <v>4.559376638725515</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146288</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.762270708614131</v>
+        <v>-4.819968942856861</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.166178442118278</v>
+        <v>2.143099148421186</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8856274724161241</v>
+        <v>0.8279292381733933</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.602819633327353</v>
+        <v>4.568200692781714</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.72380989067685</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.739897683006425</v>
+        <v>-4.797595917249155</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.122043398282532</v>
+        <v>2.09896410458544</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8968832235290256</v>
+        <v>0.8391849892862948</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.556488829916265</v>
+        <v>4.521869889370627</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739465</v>
+        <v>3.715627631739467</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.77291397891717</v>
+        <v>-4.8306122131599</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.29403508480359</v>
+        <v>2.270955791106497</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8274458468622741</v>
+        <v>0.7697476126195433</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.70002460880157</v>
+        <v>4.665405668255931</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166414</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.761386343267561</v>
+        <v>-4.819084577510291</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.290567364891682</v>
+        <v>2.26748807119459</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8864465050636365</v>
+        <v>0.8287482708209057</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.727346229550636</v>
+        <v>4.692727289004997</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.85872784460993</v>
+        <v>-4.91642607885266</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.255298876876523</v>
+        <v>2.232219583179432</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8420263228981482</v>
+        <v>0.7843280886554174</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.704362232773132</v>
+        <v>4.669743292227493</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710418</v>
+        <v>3.70522126471042</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.944583873949896</v>
+        <v>-5.002282108192627</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.222207547333375</v>
+        <v>2.199128253636283</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7996502536720131</v>
+        <v>0.7419520194292824</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.680187673430289</v>
+        <v>4.645568732884651</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893118</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.953420671366016</v>
+        <v>-5.011118905608746</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.201092030187429</v>
+        <v>2.178012736490337</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7922080810306624</v>
+        <v>0.7345098467879316</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.65814157166598</v>
+        <v>4.623522631120342</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.715564596950191</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.044803233931474</v>
+        <v>-5.102501468174204</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.174703516206295</v>
+        <v>2.151624222509203</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7008255184652041</v>
+        <v>0.6431272842224733</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.613476545171755</v>
+        <v>4.578857604626116</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171924</v>
+        <v>3.673998560171926</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.033096515944468</v>
+        <v>-5.090794750187198</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.281514461225365</v>
+        <v>2.258435167528273</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7125322364522105</v>
+        <v>0.6548340022094797</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.722628833788226</v>
+        <v>4.688009893242588</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.6824962846923</v>
+        <v>3.682496284692302</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.933433011860806</v>
+        <v>-4.991131246103536</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.324412201590236</v>
+        <v>2.301332907893143</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.775719319655897</v>
+        <v>0.7180210854131662</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.763573422441843</v>
+        <v>4.728954481896205</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,45 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.758857323081443</v>
+        <v>3.672915362735307</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.013653601053846</v>
+        <v>-5.001447344269888</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.505228799191077</v>
+        <v>2.510111301904661</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.775719319655897</v>
+        <v>0.7180210854131662</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.976478255719901</v>
+        <v>4.941859315174263</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>3.715782924255848</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>4.64174089680517</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>-5.001447344269888</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>2.510111301904661</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>0.7180210854131662</v>
+      </c>
+      <c r="G2079" t="n">
+        <v>4.634804693791538</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>152.5%</t>
+          <t>158.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.3%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>423.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-661.7%</t>
+          <t>-647.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-125.2%</t>
+          <t>-119.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.1%</t>
+          <t>587.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-307.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-138.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.279940464198855</v>
+        <v>-4.211159204700294</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.028065241780731</v>
+        <v>2.055577745580156</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9313233081456711</v>
+        <v>1.000104567644232</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.299191836661424</v>
+        <v>4.340460592360561</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.321095583767076</v>
+        <v>-4.252314324268515</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.013483824137579</v>
+        <v>2.040996327937004</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8901681885774502</v>
+        <v>0.9589494480760115</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.276379395104627</v>
+        <v>4.317648150803764</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.253047021075546</v>
+        <v>-4.184265761576985</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.053554275092074</v>
+        <v>2.081066778891498</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.95821675126898</v>
+        <v>1.026998010767541</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.330059558597427</v>
+        <v>4.371328314296564</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.484647414245047</v>
+        <v>-4.415866154746486</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.981116787997867</v>
+        <v>2.008629291797292</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.95821675126898</v>
+        <v>1.026998010767541</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.350262228771022</v>
+        <v>4.391530984470158</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.502719922536659</v>
+        <v>-4.433938663038098</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.973887784681223</v>
+        <v>2.001400288480647</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.95821675126898</v>
+        <v>1.026998010767541</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.350262228771022</v>
+        <v>4.391530984470158</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.677826755113104</v>
+        <v>-4.609045495614543</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.864096965244111</v>
+        <v>1.891609469043535</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.95821675126898</v>
+        <v>1.026998010767541</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.310514142364489</v>
+        <v>4.351782898063625</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943588</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.646540734572649</v>
+        <v>-4.577759475074088</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.883633992457233</v>
+        <v>1.911146496256658</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9895027718094354</v>
+        <v>1.058284031307997</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.336308373685702</v>
+        <v>4.377577129384838</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.493515342459364</v>
+        <v>-4.424734082960804</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.044015148875451</v>
+        <v>2.071527652674876</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.142528163922719</v>
+        <v>1.211309423421281</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.527294608526576</v>
+        <v>4.568563364225713</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073884</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.521822656332635</v>
+        <v>-4.453041396834074</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.220158448234435</v>
+        <v>2.24767095203386</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.142528163922719</v>
+        <v>1.211309423421281</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.714760833434869</v>
+        <v>4.756029589134005</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.688415881446157</v>
+        <v>-4.619634621947596</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.122924109543109</v>
+        <v>2.150436613342533</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9759349388091969</v>
+        <v>1.044716198307758</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.584207849720837</v>
+        <v>4.625476605419974</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.665380088084591</v>
+        <v>-4.59659882858603</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.135814829549453</v>
+        <v>2.163327333348877</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9759349388091969</v>
+        <v>1.044716198307758</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.587884252382555</v>
+        <v>4.629153008081691</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.636134107628894</v>
+        <v>-4.567352848130334</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.145131276855227</v>
+        <v>2.172643780654651</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9759349388091969</v>
+        <v>1.044716198307758</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.58550230750605</v>
+        <v>4.626771063205187</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.743059655506745</v>
+        <v>-4.674278396008185</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.099654296861721</v>
+        <v>2.127166800661146</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8690093909313455</v>
+        <v>0.9377906504299068</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.518640217936975</v>
+        <v>4.559908973636111</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.888078214013994</v>
+        <v>-4.819296954515433</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.043075675602056</v>
+        <v>2.07058817940148</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.723990832424097</v>
+        <v>0.7927720919226583</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.43305788497586</v>
+        <v>4.474326640674996</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.006419979798712</v>
+        <v>-4.937638720300151</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.095670208545922</v>
+        <v>2.123182712345346</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.8034581304855484</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.539400747371347</v>
+        <v>4.580669503070483</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.05783040211942</v>
+        <v>-4.989049142620859</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.072891736743578</v>
+        <v>2.100404240543002</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.8034581304855484</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.537186444497285</v>
+        <v>4.578455200196422</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.137249853327171</v>
+        <v>-5.06846859382861</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.041027084334766</v>
+        <v>2.068539588134191</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.8034581304855484</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.537089572571575</v>
+        <v>4.578358328270712</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.232712851244389</v>
+        <v>-5.163931591745828</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.002835778725923</v>
+        <v>2.030348282525347</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7346768709869871</v>
+        <v>0.8034581304855484</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.537083466129618</v>
+        <v>4.578352221828755</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.168336940393674</v>
+        <v>-5.099555680895113</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.02668253962882</v>
+        <v>2.054195043428244</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7990527818377022</v>
+        <v>0.8678340413362635</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.573805409202658</v>
+        <v>4.615074164901795</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.223706102525868</v>
+        <v>-5.154924843027307</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.010268692523669</v>
+        <v>2.037781196323093</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7990527818377022</v>
+        <v>0.8678340413362635</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.579539226950384</v>
+        <v>4.620807982649522</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396014</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.269143882356695</v>
+        <v>-5.200362622858134</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.991631943934271</v>
+        <v>2.019144447733695</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8249890506581039</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.553370595886422</v>
+        <v>4.594639351585559</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396423</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.180937048209117</v>
+        <v>-5.112155788710556</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.046789070443621</v>
+        <v>2.074301574243045</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8249890506581039</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.573244988736741</v>
+        <v>4.614513744435878</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299178</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.074902053003807</v>
+        <v>-5.006120793505247</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.072903769050473</v>
+        <v>2.100416272849897</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8249890506581039</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.556945689261469</v>
+        <v>4.598214444960606</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590409</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.891690389870712</v>
+        <v>-4.822909130372151</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.148619383767756</v>
+        <v>2.17613188756718</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7562077911595426</v>
+        <v>0.8249890506581039</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.559376638725515</v>
+        <v>4.600645394424651</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146288</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.819968942856861</v>
+        <v>-4.7511876833583</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.143099148421186</v>
+        <v>2.17061165222061</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8279292381733933</v>
+        <v>0.8967104976719545</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.568200692781714</v>
+        <v>4.60946944848085</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72380989067685</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.797595917249155</v>
+        <v>-4.728814657750594</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.09896410458544</v>
+        <v>2.126476608384865</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8391849892862948</v>
+        <v>0.9079662487848561</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.521869889370627</v>
+        <v>4.563138645069763</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739467</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.8306122131599</v>
+        <v>-4.761830953661339</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.270955791106497</v>
+        <v>2.298468294905922</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7697476126195433</v>
+        <v>0.8385288721181046</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.665405668255931</v>
+        <v>4.706674423955068</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166414</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.819084577510291</v>
+        <v>-4.75030331801173</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.26748807119459</v>
+        <v>2.295000574994015</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8287482708209057</v>
+        <v>0.897529530319467</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.692727289004997</v>
+        <v>4.733996044704135</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.91642607885266</v>
+        <v>-4.847644819354099</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.232219583179432</v>
+        <v>2.259732086978856</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7843280886554174</v>
+        <v>0.8531093481539787</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.669743292227493</v>
+        <v>4.71101204792663</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70522126471042</v>
+        <v>3.705221264710418</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.002282108192627</v>
+        <v>-4.790535383526797</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.199128253636283</v>
+        <v>2.283826943502615</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7419520194292824</v>
+        <v>0.8832647363689639</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.645568732884651</v>
+        <v>4.730356363048459</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893118</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.011118905608746</v>
+        <v>-4.799372180942917</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.178012736490337</v>
+        <v>2.262711426356669</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7345098467879316</v>
+        <v>0.8758225637276131</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.623522631120342</v>
+        <v>4.708310261284151</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950191</v>
+        <v>3.71556459695019</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.102501468174204</v>
+        <v>-4.890754743508375</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.151624222509203</v>
+        <v>2.236322912375535</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6431272842224733</v>
+        <v>0.7844400011621548</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.578857604626116</v>
+        <v>4.663645234789925</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171926</v>
+        <v>3.673998560171925</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.090794750187198</v>
+        <v>-4.879048025521369</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.258435167528273</v>
+        <v>2.343133857394605</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6548340022094797</v>
+        <v>0.7961467191491612</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.688009893242588</v>
+        <v>4.772797523406397</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.991131246103536</v>
+        <v>-4.779384521437707</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.301332907893143</v>
+        <v>2.386031597759475</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.8593338023528477</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.728954481896205</v>
+        <v>4.813742112060014</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672915362735307</v>
+        <v>3.672915362735306</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.001447344269888</v>
+        <v>-4.859605110630747</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.510111301904661</v>
+        <v>2.566848195360317</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.8593338023528477</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.941859315174263</v>
+        <v>5.026646945338072</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.715782924255848</v>
+        <v>3.759688691572987</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.64174089680517</v>
+        <v>4.697842088679622</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.001447344269888</v>
+        <v>-4.859605110630747</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.510111301904661</v>
+        <v>2.566848195360317</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.7180210854131662</v>
+        <v>0.8593338023528477</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.634804693791538</v>
+        <v>4.69090588566599</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>158.2%</t>
+          <t>147.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.4%</t>
+          <t>423.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-647.5%</t>
+          <t>-659.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-119.5%</t>
+          <t>-124.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.0%</t>
+          <t>588.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.8%</t>
+          <t>-308.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-138.1%</t>
+          <t>-144.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
     </row>
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.211159204700294</v>
+        <v>-4.222242229956125</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.055577745580156</v>
+        <v>2.051144535477824</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.000104567644232</v>
+        <v>0.9890215423884019</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.340460592360561</v>
+        <v>4.333810777207062</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.252314324268515</v>
+        <v>-4.263397349524346</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.040996327937004</v>
+        <v>2.036563117834671</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9589494480760115</v>
+        <v>0.947866422820181</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.317648150803764</v>
+        <v>4.310998335650265</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.184265761576985</v>
+        <v>-4.195348786832816</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.081066778891498</v>
+        <v>2.076633568789165</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.026998010767541</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.371328314296564</v>
+        <v>4.364678499143066</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760316</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.415866154746486</v>
+        <v>-4.426949180002317</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.008629291797292</v>
+        <v>2.00419608169496</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.026998010767541</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.391530984470158</v>
+        <v>4.38488116931666</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.433938663038098</v>
+        <v>-4.445021688293928</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.001400288480647</v>
+        <v>1.996967078378315</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.026998010767541</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.391530984470158</v>
+        <v>4.38488116931666</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.609045495614543</v>
+        <v>-4.620128520870374</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.891609469043535</v>
+        <v>1.887176258941203</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.026998010767541</v>
+        <v>1.015914985511711</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.351782898063625</v>
+        <v>4.345133082910126</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943588</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.577759475074088</v>
+        <v>-4.588842500329918</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.911146496256658</v>
+        <v>1.906713286154325</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.058284031307997</v>
+        <v>1.047201006052166</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.377577129384838</v>
+        <v>4.37092731423134</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677826</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.424734082960804</v>
+        <v>-4.435817108216634</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.071527652674876</v>
+        <v>2.067094442572543</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.211309423421281</v>
+        <v>1.20022639816545</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.568563364225713</v>
+        <v>4.561913549072215</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.453041396834074</v>
+        <v>-4.464124422089904</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.24767095203386</v>
+        <v>2.243237741931527</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.211309423421281</v>
+        <v>1.20022639816545</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.756029589134005</v>
+        <v>4.749379773980507</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.619634621947596</v>
+        <v>-4.630717647203427</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.150436613342533</v>
+        <v>2.146003403240201</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.044716198307758</v>
+        <v>1.033633173051928</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.625476605419974</v>
+        <v>4.618826790266476</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568383</v>
+        <v>3.708202704568385</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.59659882858603</v>
+        <v>-4.607681853841861</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.163327333348877</v>
+        <v>2.158894123246545</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.044716198307758</v>
+        <v>1.033633173051928</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.629153008081691</v>
+        <v>4.622503192928193</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682205</v>
+        <v>3.740601586682207</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.567352848130334</v>
+        <v>-4.578435873386164</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.172643780654651</v>
+        <v>2.168210570552319</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.044716198307758</v>
+        <v>1.033633173051928</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.626771063205187</v>
+        <v>4.620121248051689</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.69942482753911</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.674278396008185</v>
+        <v>-4.685361421264015</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.127166800661146</v>
+        <v>2.122733590558814</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9377906504299068</v>
+        <v>0.9267076251740763</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.559908973636111</v>
+        <v>4.553259158482613</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.68996278598374</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.819296954515433</v>
+        <v>-4.830379979771264</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.07058817940148</v>
+        <v>2.066154969299149</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7927720919226583</v>
+        <v>0.7816890666668278</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.474326640674996</v>
+        <v>4.467676825521498</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969751</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.937638720300151</v>
+        <v>-4.948721745555981</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.123182712345346</v>
+        <v>2.118749502243015</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8034581304855484</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.580669503070483</v>
+        <v>4.574019687916985</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073541</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.989049142620859</v>
+        <v>-5.000132167876689</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.100404240543002</v>
+        <v>2.09597103044067</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8034581304855484</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.578455200196422</v>
+        <v>4.571805385042923</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720069</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.06846859382861</v>
+        <v>-5.079551619084441</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.068539588134191</v>
+        <v>2.064106378031858</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8034581304855484</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.578358328270712</v>
+        <v>4.571708513117214</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581134</v>
+        <v>3.736825137581135</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.163931591745828</v>
+        <v>-5.175014617001659</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.030348282525347</v>
+        <v>2.025915072423015</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8034581304855484</v>
+        <v>0.7923751052297179</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.578352221828755</v>
+        <v>4.571702406675257</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500736</v>
+        <v>3.715393145500737</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.099555680895113</v>
+        <v>-5.110638706150944</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.054195043428244</v>
+        <v>2.049761833325912</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.8678340413362635</v>
+        <v>0.856751016080433</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.615074164901795</v>
+        <v>4.608424349748296</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636271</v>
+        <v>3.736109598636273</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.154924843027307</v>
+        <v>-5.166007868283137</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.037781196323093</v>
+        <v>2.033347986220761</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.8678340413362635</v>
+        <v>0.856751016080433</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.620807982649522</v>
+        <v>4.614158167496023</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396016</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.200362622858134</v>
+        <v>-5.211445648113965</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.019144447733695</v>
+        <v>2.014711237631363</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8249890506581039</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.594639351585559</v>
+        <v>4.58798953643206</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396424</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.112155788710556</v>
+        <v>-5.123238813966386</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.074301574243045</v>
+        <v>2.069868364140713</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8249890506581039</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.614513744435878</v>
+        <v>4.607863929282379</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299178</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.006120793505247</v>
+        <v>-5.017203818761077</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.100416272849897</v>
+        <v>2.095983062747565</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8249890506581039</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.598214444960606</v>
+        <v>4.591564629807107</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590409</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.822909130372151</v>
+        <v>-4.833992155627982</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.17613188756718</v>
+        <v>2.171698677464848</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8249890506581039</v>
+        <v>0.8139060254022734</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.600645394424651</v>
+        <v>4.593995579271152</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146288</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.7511876833583</v>
+        <v>-4.762270708614131</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.17061165222061</v>
+        <v>2.166178442118278</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8967104976719545</v>
+        <v>0.8856274724161241</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.60946944848085</v>
+        <v>4.602819633327353</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.72380989067685</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.728814657750594</v>
+        <v>-4.739897683006425</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.126476608384865</v>
+        <v>2.122043398282532</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9079662487848561</v>
+        <v>0.8968832235290256</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.563138645069763</v>
+        <v>4.556488829916265</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739465</v>
+        <v>3.715627631739467</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.761830953661339</v>
+        <v>-4.77291397891717</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.298468294905922</v>
+        <v>2.29403508480359</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8385288721181046</v>
+        <v>0.8274458468622741</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.706674423955068</v>
+        <v>4.70002460880157</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166414</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.75030331801173</v>
+        <v>-4.761386343267561</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.295000574994015</v>
+        <v>2.290567364891682</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.897529530319467</v>
+        <v>0.8864465050636365</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.733996044704135</v>
+        <v>4.727346229550636</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.847644819354099</v>
+        <v>-4.85872784460993</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.259732086978856</v>
+        <v>2.255298876876523</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8531093481539787</v>
+        <v>0.8420263228981482</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.71101204792663</v>
+        <v>4.704362232773132</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710418</v>
+        <v>3.70522126471042</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.790535383526797</v>
+        <v>-4.944583873949896</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.283826943502615</v>
+        <v>2.222207547333375</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8832647363689639</v>
+        <v>0.7996502536720131</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.730356363048459</v>
+        <v>4.680187673430289</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893118</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.799372180942917</v>
+        <v>-4.920950920907875</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.262711426356669</v>
+        <v>2.214079930370685</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8758225637276131</v>
+        <v>0.8107639708341773</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.708310261284151</v>
+        <v>4.669275105548089</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71556459695019</v>
+        <v>3.715564596950191</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.890754743508375</v>
+        <v>-5.012333483473333</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.236322912375535</v>
+        <v>2.187691416389551</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7844400011621548</v>
+        <v>0.7193814082687191</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.663645234789925</v>
+        <v>4.624610079053864</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171925</v>
+        <v>3.673998560171926</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.879048025521369</v>
+        <v>-5.000626765486327</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.343133857394605</v>
+        <v>2.294502361408622</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7961467191491612</v>
+        <v>0.7310881262557255</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.772797523406397</v>
+        <v>4.733762367670336</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.779384521437707</v>
+        <v>-4.900963261402665</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.386031597759475</v>
+        <v>2.337400101773492</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8593338023528477</v>
+        <v>0.794275209459412</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.813742112060014</v>
+        <v>4.774706956323953</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672915362735306</v>
+        <v>3.672915362735307</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.859605110630747</v>
+        <v>-4.981183850595706</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.566848195360317</v>
+        <v>2.518216699374333</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8593338023528477</v>
+        <v>0.794275209459412</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.026646945338072</v>
+        <v>4.987611789602011</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.759688691572987</v>
+        <v>3.688815020631034</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.697842088679622</v>
+        <v>4.586837121871145</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.859605110630747</v>
+        <v>-4.981183850595706</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.566848195360317</v>
+        <v>2.518216699374333</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8593338023528477</v>
+        <v>0.794275209459412</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.69090588566599</v>
+        <v>4.579900918857513</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>147.1%</t>
+          <t>159.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-39.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.0%</t>
+          <t>423.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.7%</t>
+          <t>-669.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-124.4%</t>
+          <t>-128.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.0%</t>
+          <t>588.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.1%</t>
+          <t>-300.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-144.6%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
     </row>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.75159294266308</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.9724698075075837</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.733879255785214</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9802338661760699</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.610404984472196</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>1.026621645921271</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.390384186435186</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.116209002146689</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.257516497371908</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.185250260573823</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.137343414007409</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.234465338359925</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.002090052677432</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.298654785453355</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.061964880035124</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.260742345911704</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-3.942144649124287</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.323959607510248</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-3.944614355586093</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.230615924247967</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.012984541910103</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.122529711203665</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.124856821536254</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.068217507985096</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.180376897428843</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.183040314320262</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.004902637636373</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.257797250229038</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-3.996978263051459</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.23670902882421</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-3.99070006048161</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.1677586232536</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-3.930847441277887</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.201872057367221</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.84460397825151</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.231315713151633</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.88991079765049</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.204968760836566</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-3.918943902352791</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.193907391988747</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.826133420901932</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.160304276460456</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.87052289023136</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.144421964653286</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-3.987064495336702</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.092881031122872</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.026988589919274</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.082402689120511</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.054768987820626</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.082787731728509</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.173149660550765</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8737911826371065</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.281763738994096</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.9504952119789798</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.246354700745953</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9791718533805598</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.207971038187802</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.991944759746189</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.030854708152636</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.059520320605557</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.075946952986182</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.042166814434052</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.896571531747414</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.107703958235974</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-3.94158574526802</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.070505728159321</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.208590255540456</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9693954863892924</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.309788036977628</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.9281202957109247</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.303277070363316</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.9283246439109665</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.284238942656018</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.9324646142021304</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.336754744930839</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>1.030752694926393</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.350621506264757</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>1.026039319378959</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.394721590386775</v>
+        <v>-4.310138514342412</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014407816127078</v>
+        <v>1.048241046544823</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.275284148486834</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>0.9601330141642532</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.2560333599063282</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.824223113816532</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.359105369761533</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.9293981471858548</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.2560333599063282</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.827016735348013</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.352952663708749</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.9325215779986269</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.2621860659591125</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.831370707371342</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.36976196185925</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.9248783354785364</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.2453767678086108</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.820365605221151</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.307463963083128</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>1.016133088785806</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.2906710320830529</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.913877717582637</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-4.10567376541797</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.8991411695659965</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.4886892242522073</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.834980634598257</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.156560478104165</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.9490767168136938</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.4378025115660127</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.874738839308715</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-4.069949735454358</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>0.9983487499896602</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.5164282427711711</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.936542014147854</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.130159033459643</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>0.9728010116122179</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.4562189447658865</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.898952416169355</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-4.080972384775292</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>0.9909672891258869</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.4562189447658865</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.897444034209284</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-4.036599253136723</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>1.008579409216751</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5005920764044551</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.923930780627861</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-4.059079603995608</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>0.9939810630117871</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5005920764044551</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.918324574766451</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-4.011423873434552</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>1.019425112264014</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.5482478069655108</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>2.953299770130889</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.910905714935797</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.064524749038241</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.6487659654642653</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.018503038604867</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.895000385503445</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.057641553287054</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.5696533047550265</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>2.957790114655196</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.850161983895047</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.079674616541042</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.574196737699896</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>2.964613877032746</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.869660440137055</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.076036173675317</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.5261120964199917</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.939924031895881</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.825457603051154</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.099596911037514</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.5703149335058921</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>2.972325336675259</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.833017268888201</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.094983045171943</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.6251183375157114</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.003617379550398</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.674725851348929</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.209547377370691</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.6251183375157114</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.054865144733438</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.467083847714453</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.291044883418735</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.8327603411501876</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.177891051508376</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.416051754991925</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.306405948746016</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.8837924338727156</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.203458535380163</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.350827573864719</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.349683025289603</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>0.9490166149999212</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.259780448149192</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.313400553793585</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.360614805617337</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>0.9542681530291028</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.258892343265981</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.333512209828294</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.353826935534694</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>0.965295498026522</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.266765542595673</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.30509894672841</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.525750011795858</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>0.9063199352800932</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.391937975969026</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.230316685703397</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.675775825423681</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>0.9811021963051059</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.556920241801851</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.204232601439589</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.677917435143063</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>0.9811021963051059</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.54862821781571</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.116354688330469</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.711261795970491</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.097027838728457</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.6163767988535</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.107462226937185</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.732373186254595</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.097027838728457</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.633931204580292</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.275938343907063</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.656837786871228</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.069080003011876</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.609017550554927</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.829682151277623</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.816609961110866</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>0.9743613333422436</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.533456045941009</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.806961047594471</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.816362425081032</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>0.9743613333422436</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.524120068437914</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.936162860888513</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.923587825614583</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.8451595200482014</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.605505106312658</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.962037259362539</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.95031588871862</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>0.8900711287599425</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.669529894033349</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.954982569147365</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.949813120794234</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.8971258189751163</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.670438064151998</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.928031344820877</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>1.970599764169571</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9120061650028355</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.689372425413371</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.949575572651665</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.146085205182216</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9120061650028355</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.873475557558331</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.971983690456537</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.12923865296326</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>0.9120061650028355</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.865592252461324</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-3.000207926034137</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.120002958281858</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>0.9299829174541441</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.878432303481747</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-3.009648851922667</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.172480305648293</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.052410034997536</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.008142291729629</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.070219954756078</v>
+        <v>-3.098525483091141</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.15114295906023</v>
+        <v>2.139820747726204</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.067414134947334</v>
+        <v>0.9635334038290617</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.020035846244808</v>
+        <v>3.957707407573846</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.146549932356984</v>
+        <v>-3.174855460692047</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.118722780913642</v>
+        <v>2.107400569579617</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.067414134947334</v>
+        <v>0.9635334038290617</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.018147659138584</v>
+        <v>3.955819220467621</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.240213877034526</v>
+        <v>-3.268519405369588</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.076077432645488</v>
+        <v>2.064755221311463</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9737501902697926</v>
+        <v>0.8698694591515203</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956769521934921</v>
+        <v>3.894441083263958</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.401782302561781</v>
+        <v>-3.430087830896843</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.009884072644738</v>
+        <v>1.998561861310713</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.7430865353536409</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.879133777866346</v>
+        <v>3.816805339195382</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.5100829644319</v>
+        <v>-3.538388492766963</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.979637214762609</v>
+        <v>1.968315003428584</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.7430865353536409</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.892207184732265</v>
+        <v>3.829878746061302</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.527886936152644</v>
+        <v>-3.556192464487707</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.964520822857251</v>
+        <v>1.953198611523226</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7764326435667122</v>
+        <v>0.6725519124484398</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.841891607772084</v>
+        <v>3.779563169101121</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.555787723262117</v>
+        <v>-3.58409325159718</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.951884549140464</v>
+        <v>1.940562337806439</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7418357194237774</v>
+        <v>0.637954988305505</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.819657494413325</v>
+        <v>3.757329055742362</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.678313825965011</v>
+        <v>-3.706619354300074</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.899638552036506</v>
+        <v>1.88831634070248</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6193096167208835</v>
+        <v>0.5154288856026111</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.742906276768788</v>
+        <v>3.680577838097824</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.9088283221506</v>
+        <v>-3.937133850485663</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.874138713152774</v>
+        <v>1.862816501818748</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3887951205352947</v>
+        <v>0.2849143894170224</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.671303538647938</v>
+        <v>3.608975099976975</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.257573407375044</v>
+        <v>-4.285878935710106</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.874952398064843</v>
+        <v>1.863630186730818</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.1761664354981246</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.746366485298446</v>
+        <v>3.684038046627483</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.411559825151184</v>
+        <v>-4.439865353486247</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.882338100100027</v>
+        <v>1.871015888766002</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.1761664354981246</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.815346754444086</v>
+        <v>3.753018315773123</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.361037921323518</v>
+        <v>-4.389343449658581</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.888598063751214</v>
+        <v>1.877275852417189</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.1761664354981246</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.801397956564207</v>
+        <v>3.739069517893244</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.613513075331243</v>
+        <v>-4.641818603666305</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.799478491203538</v>
+        <v>1.788156279869513</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.1761664354981246</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.813268445619621</v>
+        <v>3.750940006948658</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.906408831810655</v>
+        <v>-4.934714360145717</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.683530723130717</v>
+        <v>1.672208511796692</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2800471666163969</v>
+        <v>0.1761664354981246</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.814478980138565</v>
+        <v>3.752150541467601</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.093072959945463</v>
+        <v>-5.121378488280525</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.612986814104115</v>
+        <v>1.60166460277009</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2533081957918371</v>
+        <v>0.1494274646735647</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.802557339871151</v>
+        <v>3.740228901200187</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.239093646859425</v>
+        <v>-5.267399175194488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.54965639207472</v>
+        <v>1.538334180740695</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2442251039979801</v>
+        <v>0.1403443728797077</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.792185337531026</v>
+        <v>3.729856898860062</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.330807655969011</v>
+        <v>-5.359113184304072</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.67517484512993</v>
+        <v>1.663852633795905</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2442251039979801</v>
+        <v>0.1403443728797077</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.95438939423007</v>
+        <v>3.892060955559106</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.36245931502898</v>
+        <v>-5.390764843364042</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.657360819469756</v>
+        <v>1.646038608135731</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2390566467535399</v>
+        <v>0.1351759156352675</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.94613495784722</v>
+        <v>3.883806519176257</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.444394133297863</v>
+        <v>-5.472699661632925</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.634816309730694</v>
+        <v>1.623494098396669</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2291219011664597</v>
+        <v>0.1252411700481874</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.950403528063463</v>
+        <v>3.888075089392499</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.546370255546271</v>
+        <v>-5.574675783881332</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.602951499287233</v>
+        <v>1.591629287953209</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1271457789180521</v>
+        <v>0.02326504779977978</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.898143493170321</v>
+        <v>3.835815054499357</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.436363972069049</v>
+        <v>-5.464669500404111</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.639106899922298</v>
+        <v>1.627784688588273</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1503503508353273</v>
+        <v>0.04646961971705499</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.904219123564861</v>
+        <v>3.841890684893898</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.293304396328123</v>
+        <v>-5.321609924663185</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.700580740940642</v>
+        <v>1.689258529606617</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1583637774253066</v>
+        <v>0.05448304630703427</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.913277190240823</v>
+        <v>3.850948751569859</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.991857670856286</v>
+        <v>-5.020163199191347</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.828420314011913</v>
+        <v>1.817098102677889</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4598105028971439</v>
+        <v>0.3559297717788715</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.101406108406461</v>
+        <v>4.039077669735498</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.01644791509147</v>
+        <v>-5.044753443426531</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.81955539407055</v>
+        <v>1.808233182736525</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4598105028971439</v>
+        <v>0.3559297717788715</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.102377286159172</v>
+        <v>4.040048847488209</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.965409539084949</v>
+        <v>-4.993715067420011</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.840813648852914</v>
+        <v>1.829491437518889</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4598105028971439</v>
+        <v>0.3559297717788715</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.103220190538927</v>
+        <v>4.040891751867965</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.924270244218318</v>
+        <v>-4.95257577255338</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.876307465673712</v>
+        <v>1.864985254339687</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5009497977637747</v>
+        <v>0.3970690666455023</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.146941866333052</v>
+        <v>4.084613427662088</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.827635332199678</v>
+        <v>-4.85594086053474</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.731145426605102</v>
+        <v>1.719823215271077</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5975847097824146</v>
+        <v>0.4937039786641423</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.02110680966817</v>
+        <v>3.958778370997207</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.958216066730521</v>
+        <v>-4.986521595065582</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.682415176866729</v>
+        <v>1.671092965532704</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4670039752515721</v>
+        <v>0.3631232441332998</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.946260413023628</v>
+        <v>3.883931974352665</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.793719732539559</v>
+        <v>-4.822025260874621</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.732640529619197</v>
+        <v>1.721318318285172</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.631500309442534</v>
+        <v>0.5276195783242617</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.029385032614289</v>
+        <v>3.967056593943325</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.716621130997686</v>
+        <v>-4.744926659332748</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.762667680672376</v>
+        <v>1.751345469338351</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.631500309442534</v>
+        <v>0.5276195783242617</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.028572743050718</v>
+        <v>3.966244304379755</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.727006325887576</v>
+        <v>-4.755311854222637</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.768382381841492</v>
+        <v>1.757060170507467</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6211151145526447</v>
+        <v>0.5172343834343723</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.032210405241857</v>
+        <v>3.969881966570894</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.745594484609801</v>
+        <v>-4.773900012944862</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.831784124129027</v>
+        <v>1.820461912795002</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6025269558304194</v>
+        <v>0.498646224712147</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.091894515784947</v>
+        <v>4.029566077113984</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.745893031305837</v>
+        <v>-4.774198559640898</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.828533716268911</v>
+        <v>1.817211504934886</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6022284091343835</v>
+        <v>0.4983476780161111</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.088584398585624</v>
+        <v>4.026255959914661</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.645069897615409</v>
+        <v>-4.673375425950471</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.873393864684474</v>
+        <v>1.862071653350449</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6146926246187373</v>
+        <v>0.510811893500465</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.100593822815627</v>
+        <v>4.038265384144664</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.454288536863002</v>
+        <v>-4.482594065198064</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.94983566246398</v>
+        <v>1.938513451129955</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8054739853711447</v>
+        <v>0.7015932542528723</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.215191892745615</v>
+        <v>4.152863454074652</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.347325179013581</v>
+        <v>-4.375630707348642</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.972457851341345</v>
+        <v>1.961135640007321</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8639385933309461</v>
+        <v>0.7600578622126738</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.230107503259092</v>
+        <v>4.167779064588129</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.291994591111818</v>
+        <v>-4.32030011944688</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.029557023114108</v>
+        <v>2.018234811780084</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9192691812327083</v>
+        <v>0.8153884501144359</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.298272792612209</v>
+        <v>4.235944353941245</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.222242229956125</v>
+        <v>-4.308245992533917</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.051144535477824</v>
+        <v>2.016743030446706</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9890215423884019</v>
+        <v>0.8274425770273988</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.333810777207062</v>
+        <v>4.236863397990461</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.263397349524346</v>
+        <v>-4.349401112102138</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.036563117834671</v>
+        <v>2.002161612803554</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.947866422820181</v>
+        <v>0.7862874574591778</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.310998335650265</v>
+        <v>4.214050956433663</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.195348786832816</v>
+        <v>-4.281352549410608</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.076633568789165</v>
+        <v>2.042232063758048</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.015914985511711</v>
+        <v>0.8543360201507076</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.364678499143066</v>
+        <v>4.267731119926464</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.426949180002317</v>
+        <v>-4.512952942580108</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.00419608169496</v>
+        <v>1.969794576663842</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.015914985511711</v>
+        <v>0.8543360201507076</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.38488116931666</v>
+        <v>4.287933790100058</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781708</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.445021688293928</v>
+        <v>-4.53102545087172</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.996967078378315</v>
+        <v>1.962565573347198</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.015914985511711</v>
+        <v>0.8543360201507076</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.38488116931666</v>
+        <v>4.287933790100058</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082837</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.620128520870374</v>
+        <v>-4.706132283448166</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.887176258941203</v>
+        <v>1.852774753910086</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.015914985511711</v>
+        <v>0.8543360201507076</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.345133082910126</v>
+        <v>4.248185703693525</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943588</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.588842500329918</v>
+        <v>-4.67484626290771</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.906713286154325</v>
+        <v>1.872311781123208</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.047201006052166</v>
+        <v>0.885622040691163</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.37092731423134</v>
+        <v>4.273979935014738</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677826</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.435817108216634</v>
+        <v>-4.428966624662519</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.067094442572543</v>
+        <v>2.069834635994189</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.20022639816545</v>
+        <v>1.131501678936355</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.561913549072215</v>
+        <v>4.520678717534757</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.464124422089904</v>
+        <v>-4.457273938535789</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.243237741931527</v>
+        <v>2.245977935353173</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.20022639816545</v>
+        <v>1.131501678936355</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.749379773980507</v>
+        <v>4.70814494244305</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903171</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.630717647203427</v>
+        <v>-4.623867163649312</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.146003403240201</v>
+        <v>2.148743596661847</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.033633173051928</v>
+        <v>0.9649084538228323</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.618826790266476</v>
+        <v>4.577591958729019</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568385</v>
+        <v>3.708202704568383</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.607681853841861</v>
+        <v>-4.600831370287746</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.158894123246545</v>
+        <v>2.161634316668191</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.033633173051928</v>
+        <v>0.9649084538228323</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.622503192928193</v>
+        <v>4.581268361390737</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682207</v>
+        <v>3.740601586682205</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.578435873386164</v>
+        <v>-4.571585389832049</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.168210570552319</v>
+        <v>2.170950763973964</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.033633173051928</v>
+        <v>0.9649084538228323</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.620121248051689</v>
+        <v>4.578886416514232</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69942482753911</v>
+        <v>3.699424827539108</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.685361421264015</v>
+        <v>-4.6785109377099</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.122733590558814</v>
+        <v>2.125473783980459</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9267076251740763</v>
+        <v>0.8579829059449809</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.553259158482613</v>
+        <v>4.512024326945156</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.68996278598374</v>
+        <v>3.689962785983738</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.830379979771264</v>
+        <v>-4.823529496217149</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.066154969299149</v>
+        <v>2.068895162720794</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7816890666668278</v>
+        <v>0.7129643474377324</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.467676825521498</v>
+        <v>4.42644199398404</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969751</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.948721745555981</v>
+        <v>-4.941871262001866</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.118749502243015</v>
+        <v>2.12148969566466</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7236503860006225</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.574019687916985</v>
+        <v>4.532784856379528</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073541</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.000132167876689</v>
+        <v>-4.993281684322574</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.09597103044067</v>
+        <v>2.098711223862315</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7236503860006225</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.571805385042923</v>
+        <v>4.530570553505466</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720069</v>
+        <v>3.704778134720067</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.079551619084441</v>
+        <v>-5.072701135530326</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.064106378031858</v>
+        <v>2.066846571453504</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7236503860006225</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.571708513117214</v>
+        <v>4.530473681579756</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581134</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.175014617001659</v>
+        <v>-5.168164133447544</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.025915072423015</v>
+        <v>2.028655265844661</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7923751052297179</v>
+        <v>0.7236503860006225</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.571702406675257</v>
+        <v>4.530467575137799</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500737</v>
+        <v>3.715393145500736</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.110638706150944</v>
+        <v>-5.103788222596829</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.049761833325912</v>
+        <v>2.052502026747557</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.856751016080433</v>
+        <v>0.7880262968513376</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.608424349748296</v>
+        <v>4.56718951821084</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636273</v>
+        <v>3.736109598636271</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.166007868283137</v>
+        <v>-5.159157384729022</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.033347986220761</v>
+        <v>2.036088179642407</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.856751016080433</v>
+        <v>0.7880262968513376</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.614158167496023</v>
+        <v>4.572923335958566</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396016</v>
+        <v>3.736843055396014</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.211445648113965</v>
+        <v>-5.20459516455985</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.014711237631363</v>
+        <v>2.017451431053008</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.745181306173178</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.58798953643206</v>
+        <v>4.546754704894603</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396424</v>
+        <v>3.790292685396423</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.123238813966386</v>
+        <v>-5.116388330412271</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.069868364140713</v>
+        <v>2.072608557562359</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.745181306173178</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.607863929282379</v>
+        <v>4.566629097744922</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299178</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.017203818761077</v>
+        <v>-5.010353335206962</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.095983062747565</v>
+        <v>2.09872325616921</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.745181306173178</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.591564629807107</v>
+        <v>4.55032979826965</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590409</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.833992155627982</v>
+        <v>-4.827141672073867</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.171698677464848</v>
+        <v>2.174438870886494</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8139060254022734</v>
+        <v>0.745181306173178</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.593995579271152</v>
+        <v>4.552760747733696</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146288</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.762270708614131</v>
+        <v>-4.755420225060016</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.166178442118278</v>
+        <v>2.168918635539923</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8856274724161241</v>
+        <v>0.8169027531870287</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.602819633327353</v>
+        <v>4.561584801789895</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72380989067685</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.739897683006425</v>
+        <v>-4.73304719945231</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.122043398282532</v>
+        <v>2.124783591704178</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8968832235290256</v>
+        <v>0.8281585042999302</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.556488829916265</v>
+        <v>4.515253998378808</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739467</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.77291397891717</v>
+        <v>-4.766063495363055</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.29403508480359</v>
+        <v>2.296775278225236</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8274458468622741</v>
+        <v>0.7587211276331787</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.70002460880157</v>
+        <v>4.658789777264112</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166414</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.761386343267561</v>
+        <v>-4.754535859713446</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.290567364891682</v>
+        <v>2.293307558313328</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8864465050636365</v>
+        <v>0.8177217858345411</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.727346229550636</v>
+        <v>4.686111398013179</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.85872784460993</v>
+        <v>-4.851877361055815</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.255298876876523</v>
+        <v>2.258039070298169</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8420263228981482</v>
+        <v>0.7733016036690528</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.704362232773132</v>
+        <v>4.663127401235674</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70522126471042</v>
+        <v>3.705221264710418</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.944583873949896</v>
+        <v>-4.937733390395781</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.222207547333375</v>
+        <v>2.224947740755021</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7996502536720131</v>
+        <v>0.7309255344429177</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.680187673430289</v>
+        <v>4.638952841892832</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893118</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.920950920907875</v>
+        <v>-4.946570187811901</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.214079930370685</v>
+        <v>2.203832223609075</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8107639708341773</v>
+        <v>0.723483361801567</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.669275105548089</v>
+        <v>4.616906740128523</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950191</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.012333483473333</v>
+        <v>-5.037952750377359</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.187691416389551</v>
+        <v>2.177443709627941</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7193814082687191</v>
+        <v>0.6321007992361087</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.624610079053864</v>
+        <v>4.572241713634297</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171926</v>
+        <v>3.673998560171925</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.000626765486327</v>
+        <v>-5.026246032390353</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.294502361408622</v>
+        <v>2.284254654647011</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7310881262557255</v>
+        <v>0.6438075172231151</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.733762367670336</v>
+        <v>4.681394002250769</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692302</v>
+        <v>3.682496284692301</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.900963261402665</v>
+        <v>-4.994936606451944</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.337400101773492</v>
+        <v>2.29981076375378</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.794275209459412</v>
+        <v>0.6572989936562493</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.774706956323953</v>
+        <v>4.692521226842055</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.981183850595706</v>
+        <v>-5.075157195644985</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.518216699374333</v>
+        <v>2.480627361354621</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.794275209459412</v>
+        <v>0.6572989936562493</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.987611789602011</v>
+        <v>4.905426060120113</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.688815020631034</v>
+        <v>3.789144401360273</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.586837121871145</v>
+        <v>4.705832861074768</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.981183850595706</v>
+        <v>-5.075157195644985</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.518216699374333</v>
+        <v>2.480627361354621</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.794275209459412</v>
+        <v>0.6572989936562493</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.579900918857513</v>
+        <v>4.698896658061136</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>159.0%</t>
+          <t>150.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.2%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.1%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-669.1%</t>
+          <t>-642.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-128.2%</t>
+          <t>-106.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.6%</t>
+          <t>589.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-300.8%</t>
+          <t>-309.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-135.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.75159294266308</v>
+        <v>-4.836176018707442</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9724698075075837</v>
+        <v>0.9386365770898388</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.733879255785214</v>
+        <v>-4.818462331829577</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9802338661760699</v>
+        <v>0.946400635758325</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.610404984472196</v>
+        <v>-4.694988060516558</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.026621645921271</v>
+        <v>0.9927884155035258</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.390384186435186</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.116209002146689</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.257516497371908</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.185250260573823</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.137343414007409</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.234465338359925</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.002090052677432</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.298654785453355</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.061964880035124</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.260742345911704</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.942144649124287</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.323959607510248</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.944614355586093</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.230615924247967</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.012984541910103</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.122529711203665</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.124856821536254</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.068217507985096</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.180376897428843</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.183040314320262</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.004902637636373</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257797250229038</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.996978263051459</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.23670902882421</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.99070006048161</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.1677586232536</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.930847441277887</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.201872057367221</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.84460397825151</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.231315713151633</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.88991079765049</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.204968760836566</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.918943902352791</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.193907391988747</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.826133420901932</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.160304276460456</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.87052289023136</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.144421964653286</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.987064495336702</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.092881031122872</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.026988589919274</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.082402689120511</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.054768987820626</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.082787731728509</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.173149660550765</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8737911826371065</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.281763738994096</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9504952119789798</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.246354700745953</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9791718533805598</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.207971038187802</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.991944759746189</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.030854708152636</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059520320605557</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.075946952986182</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042166814434052</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.896571531747414</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.107703958235974</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.94158574526802</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.070505728159321</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.208590255540456</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9693954863892924</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.309788036977628</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9281202957109247</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.303277070363316</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9283246439109665</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.284238942656018</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9324646142021304</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.336754744930839</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.030752694926393</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.350621506264757</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.026039319378959</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.310138514342412</v>
+        <v>-4.394721590386775</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.048241046544823</v>
+        <v>1.014407816127078</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.275284148486834</v>
+        <v>-4.246978620151772</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9601330141642532</v>
+        <v>0.9714552254982785</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2560333599063282</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.824223113816532</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.359105369761533</v>
+        <v>-4.330799841426471</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9293981471858548</v>
+        <v>0.9407203585198802</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2560333599063282</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.827016735348013</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.352952663708749</v>
+        <v>-4.324647135373686</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9325215779986269</v>
+        <v>0.9438437893326523</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2621860659591125</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.831370707371342</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.36976196185925</v>
+        <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9248783354785364</v>
+        <v>0.9362005468125618</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2453767678086108</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.820365605221151</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.307463963083128</v>
+        <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.016133088785806</v>
+        <v>1.027455300119831</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2906710320830529</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.913877717582637</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.10567376541797</v>
+        <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8991411695659965</v>
+        <v>0.9104633809000218</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4886892242522073</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.834980634598257</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.156560478104165</v>
+        <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9490767168136938</v>
+        <v>0.9603989281477192</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4378025115660127</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.874738839308715</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.069949735454358</v>
+        <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9983487499896602</v>
+        <v>1.009670961323685</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5164282427711711</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.936542014147854</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.130159033459643</v>
+        <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9728010116122179</v>
+        <v>0.9841232229462431</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4562189447658865</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.898952416169355</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.080972384775292</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9909672891258869</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4562189447658865</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.897444034209284</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.036599253136723</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.008579409216751</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5005920764044551</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.923930780627861</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.059079603995608</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9939810630117871</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5005920764044551</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.918324574766451</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.011423873434552</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.019425112264014</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5482478069655108</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.953299770130889</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.910905714935797</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.064524749038241</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6487659654642653</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.018503038604867</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.895000385503445</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.057641553287054</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5696533047550265</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.957790114655196</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.850161983895047</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.079674616541042</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.574196737699896</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.964613877032746</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.869660440137055</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.076036173675317</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5261120964199917</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.939924031895881</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.825457603051154</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.099596911037514</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5703149335058921</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.972325336675259</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.833017268888201</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.094983045171943</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6251183375157114</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.003617379550398</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.674725851348929</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.209547377370691</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6251183375157114</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.054865144733438</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.467083847714453</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291044883418735</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8327603411501876</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.177891051508376</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.416051754991925</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.306405948746016</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8837924338727156</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.203458535380163</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.350827573864719</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.349683025289603</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9490166149999212</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.259780448149192</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.313400553793585</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.360614805617337</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9542681530291028</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.258892343265981</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.333512209828294</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.353826935534694</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.965295498026522</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.266765542595673</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.30509894672841</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.525750011795858</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9063199352800932</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.391937975969026</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.230316685703397</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.675775825423681</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9811021963051059</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.556920241801851</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.204232601439589</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.677917435143063</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9811021963051059</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.54862821781571</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.116354688330469</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.711261795970491</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.097027838728457</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.6163767988535</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.107462226937185</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.732373186254595</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.097027838728457</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.633931204580292</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.275938343907063</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.656837786871228</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.069080003011876</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.609017550554927</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.829682151277623</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.816609961110866</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9743613333422436</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.533456045941009</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.806961047594471</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.816362425081032</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9743613333422436</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.524120068437914</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.936162860888513</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.923587825614583</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8451595200482014</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.605505106312658</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.962037259362539</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.95031588871862</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8900711287599425</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.669529894033349</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.954982569147365</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.949813120794234</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8971258189751163</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.670438064151998</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.928031344820877</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.970599764169571</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9120061650028355</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.689372425413371</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.949575572651665</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.146085205182216</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9120061650028355</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.873475557558331</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.971983690456537</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.12923865296326</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9120061650028355</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.865592252461324</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.000207926034137</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.120002958281858</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9299829174541441</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.878432303481747</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.009648851922667</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.172480305648293</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.052410034997536</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.008142291729629</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.098525483091141</v>
+        <v>-3.024466795141434</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.139820747726204</v>
+        <v>2.169444222906087</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9635334038290617</v>
+        <v>1.113167294561979</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.957707407573846</v>
+        <v>4.047487742013596</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.174855460692047</v>
+        <v>-3.10079677274234</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.107400569579617</v>
+        <v>2.1370240447595</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9635334038290617</v>
+        <v>1.113167294561979</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.955819220467621</v>
+        <v>4.045599554907371</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.268519405369588</v>
+        <v>-3.141238229550369</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.064755221311463</v>
+        <v>2.115667691639151</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8698694591515203</v>
+        <v>1.072725837753949</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.894441083263958</v>
+        <v>4.016154910425415</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.430087830896843</v>
+        <v>-3.302806655077624</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.998561861310713</v>
+        <v>2.049474331638401</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7430865353536409</v>
+        <v>0.9459429139560699</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.816805339195382</v>
+        <v>3.93851916635684</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.538388492766963</v>
+        <v>-3.411107316947743</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.968315003428584</v>
+        <v>2.019227473756272</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7430865353536409</v>
+        <v>0.9459429139560699</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.829878746061302</v>
+        <v>3.951592573222759</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.556192464487707</v>
+        <v>-3.428911288668488</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.953198611523226</v>
+        <v>2.004111081850914</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6725519124484398</v>
+        <v>0.8754082910508687</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.779563169101121</v>
+        <v>3.901276996262578</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.58409325159718</v>
+        <v>-3.456812075777961</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.940562337806439</v>
+        <v>1.991474808134127</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.637954988305505</v>
+        <v>0.8408113669079339</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.757329055742362</v>
+        <v>3.879042882903819</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.706619354300074</v>
+        <v>-3.579338178480854</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.88831634070248</v>
+        <v>1.939228811030168</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5154288856026111</v>
+        <v>0.71828526420504</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.680577838097824</v>
+        <v>3.802291665259282</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.937133850485663</v>
+        <v>-3.809852674666443</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.862816501818748</v>
+        <v>1.913728972146437</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2849143894170224</v>
+        <v>0.4877707680194513</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.608975099976975</v>
+        <v>3.730688927138432</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.285878935710106</v>
+        <v>-4.158597759890887</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.863630186730818</v>
+        <v>1.914542657058506</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1761664354981246</v>
+        <v>0.3790228141005535</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.684038046627483</v>
+        <v>3.80575187378894</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.439865353486247</v>
+        <v>-4.312584177667027</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.871015888766002</v>
+        <v>1.92192835909369</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1761664354981246</v>
+        <v>0.3790228141005535</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.753018315773123</v>
+        <v>3.87473214293458</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.389343449658581</v>
+        <v>-4.262062273839361</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.877275852417189</v>
+        <v>1.928188322744877</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1761664354981246</v>
+        <v>0.3790228141005535</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.739069517893244</v>
+        <v>3.860783345054701</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.641818603666305</v>
+        <v>-4.514537427847086</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.788156279869513</v>
+        <v>1.839068750197201</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1761664354981246</v>
+        <v>0.3790228141005535</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.750940006948658</v>
+        <v>3.872653834110115</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.934714360145717</v>
+        <v>-4.807433184326498</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.672208511796692</v>
+        <v>1.72312098212438</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1761664354981246</v>
+        <v>0.3790228141005535</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.752150541467601</v>
+        <v>3.873864368629059</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.121378488280525</v>
+        <v>-4.994097312461306</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.60166460277009</v>
+        <v>1.652577073097778</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1494274646735647</v>
+        <v>0.3522838432759936</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.740228901200187</v>
+        <v>3.861942728361644</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.267399175194488</v>
+        <v>-5.140117999375268</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.538334180740695</v>
+        <v>1.589246651068383</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1403443728797077</v>
+        <v>0.3432007514821366</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.729856898860062</v>
+        <v>3.85157072602152</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.359113184304072</v>
+        <v>-5.231832008484853</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.663852633795905</v>
+        <v>1.714765104123593</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1403443728797077</v>
+        <v>0.3432007514821366</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.892060955559106</v>
+        <v>4.013774782720564</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.390764843364042</v>
+        <v>-5.263483667544822</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.646038608135731</v>
+        <v>1.69695107846342</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1351759156352675</v>
+        <v>0.3380322942376964</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.883806519176257</v>
+        <v>4.005520346337714</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.472699661632925</v>
+        <v>-5.345418485813705</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.623494098396669</v>
+        <v>1.674406568724357</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1252411700481874</v>
+        <v>0.3280975486506162</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.888075089392499</v>
+        <v>4.009788916553957</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.574675783881332</v>
+        <v>-5.447394608062113</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.591629287953209</v>
+        <v>1.642541758280897</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.02326504779977978</v>
+        <v>0.2261214264022087</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.835815054499357</v>
+        <v>3.957528881660815</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.464669500404111</v>
+        <v>-5.337388324584891</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.627784688588273</v>
+        <v>1.678697158915961</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.04646961971705499</v>
+        <v>0.2493259983194839</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.841890684893898</v>
+        <v>3.963604512055355</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.321609924663185</v>
+        <v>-5.194328748843965</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.689258529606617</v>
+        <v>1.740170999934306</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.05448304630703427</v>
+        <v>0.2573394249094632</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.850948751569859</v>
+        <v>3.972662578731317</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.020163199191347</v>
+        <v>-4.892882023372128</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.817098102677889</v>
+        <v>1.868010573005576</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3559297717788715</v>
+        <v>0.5587861503813004</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.039077669735498</v>
+        <v>4.160791496896955</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.044753443426531</v>
+        <v>-4.917472267607311</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.808233182736525</v>
+        <v>1.859145653064214</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3559297717788715</v>
+        <v>0.5587861503813004</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.040048847488209</v>
+        <v>4.161762674649666</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.993715067420011</v>
+        <v>-4.866433891600791</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.829491437518889</v>
+        <v>1.880403907846577</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3559297717788715</v>
+        <v>0.5587861503813004</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.040891751867965</v>
+        <v>4.162605579029422</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.95257577255338</v>
+        <v>-4.82529459673416</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.864985254339687</v>
+        <v>1.915897724667375</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3970690666455023</v>
+        <v>0.5999254452479312</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.084613427662088</v>
+        <v>4.206327254823545</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.85594086053474</v>
+        <v>-4.72865968471552</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.719823215271077</v>
+        <v>1.770735685598765</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4937039786641423</v>
+        <v>0.6965603572665712</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.958778370997207</v>
+        <v>4.080492198158664</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.986521595065582</v>
+        <v>-4.859240419246363</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.671092965532704</v>
+        <v>1.722005435860393</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3631232441332998</v>
+        <v>0.5659796227357287</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.883931974352665</v>
+        <v>4.005645801514122</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.822025260874621</v>
+        <v>-4.694744085055401</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.721318318285172</v>
+        <v>1.77223078861286</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5276195783242617</v>
+        <v>0.7304759569266905</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.967056593943325</v>
+        <v>4.088770421104782</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.744926659332748</v>
+        <v>-4.617645483513528</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.751345469338351</v>
+        <v>1.802257939666039</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5276195783242617</v>
+        <v>0.7304759569266905</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.966244304379755</v>
+        <v>4.087958131541212</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.755311854222637</v>
+        <v>-4.628030678403418</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.757060170507467</v>
+        <v>1.807972640835156</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5172343834343723</v>
+        <v>0.7200907620368012</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.969881966570894</v>
+        <v>4.091595793732351</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.773900012944862</v>
+        <v>-4.646618837125643</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.820461912795002</v>
+        <v>1.871374383122691</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.498646224712147</v>
+        <v>0.7015026033145759</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.029566077113984</v>
+        <v>4.151279904275441</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.774198559640898</v>
+        <v>-4.646917383821679</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.817211504934886</v>
+        <v>1.868123975262575</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4983476780161111</v>
+        <v>0.70120405661854</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.026255959914661</v>
+        <v>4.147969787076118</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.673375425950471</v>
+        <v>-4.546094250131251</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.862071653350449</v>
+        <v>1.912984123678137</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.510811893500465</v>
+        <v>0.7136682721028939</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.038265384144664</v>
+        <v>4.159979211306122</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.482594065198064</v>
+        <v>-4.355312889378844</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.938513451129955</v>
+        <v>1.989425921457643</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7015932542528723</v>
+        <v>0.9044496328553012</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.152863454074652</v>
+        <v>4.274577281236109</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.375630707348642</v>
+        <v>-4.248349531529422</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.961135640007321</v>
+        <v>2.012048110335009</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7600578622126738</v>
+        <v>0.9629142408151027</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.167779064588129</v>
+        <v>4.289492891749586</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.32030011944688</v>
+        <v>-4.19301894362766</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.018234811780084</v>
+        <v>2.069147282107772</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8153884501144359</v>
+        <v>1.018244828716865</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.235944353941245</v>
+        <v>4.357658181102702</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.308245992533917</v>
+        <v>-4.180964816714697</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.016743030446706</v>
+        <v>2.067655500774395</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8274425770273988</v>
+        <v>1.030298955629828</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.236863397990461</v>
+        <v>4.358577225151918</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.349401112102138</v>
+        <v>-4.222119936282918</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.002161612803554</v>
+        <v>2.053074083131242</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7862874574591778</v>
+        <v>0.9891438360616067</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.214050956433663</v>
+        <v>4.335764783595121</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.281352549410608</v>
+        <v>-4.154071373591388</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.042232063758048</v>
+        <v>2.093144534085737</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8543360201507076</v>
+        <v>1.057192398753136</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.267731119926464</v>
+        <v>4.389444947087921</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.512952942580108</v>
+        <v>-4.385671766760889</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.969794576663842</v>
+        <v>2.02070704699153</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8543360201507076</v>
+        <v>1.057192398753136</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.287933790100058</v>
+        <v>4.409647617261515</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.53102545087172</v>
+        <v>-4.4037442750525</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.962565573347198</v>
+        <v>2.013478043674886</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8543360201507076</v>
+        <v>1.057192398753136</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.287933790100058</v>
+        <v>4.409647617261515</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.706132283448166</v>
+        <v>-4.578851107628946</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.852774753910086</v>
+        <v>1.903687224237774</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8543360201507076</v>
+        <v>1.057192398753136</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.248185703693525</v>
+        <v>4.369899530854982</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943588</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.67484626290771</v>
+        <v>-4.547565087088491</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.872311781123208</v>
+        <v>1.923224251450896</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.885622040691163</v>
+        <v>1.088478419293592</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.273979935014738</v>
+        <v>4.395693762176196</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.428966624662519</v>
+        <v>-4.394539694975206</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.069834635994189</v>
+        <v>2.083605407869115</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.131501678936355</v>
+        <v>1.241503811406876</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.520678717534757</v>
+        <v>4.58667999701707</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.457273938535789</v>
+        <v>-4.422847008848477</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.245977935353173</v>
+        <v>2.259748707228098</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.131501678936355</v>
+        <v>1.241503811406876</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.70814494244305</v>
+        <v>4.774146221925363</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.623867163649312</v>
+        <v>-4.589440233961999</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.148743596661847</v>
+        <v>2.162514368536772</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9649084538228323</v>
+        <v>1.074910586293353</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.577591958729019</v>
+        <v>4.643593238211331</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568383</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.600831370287746</v>
+        <v>-4.566404440600433</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.161634316668191</v>
+        <v>2.175405088543116</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9649084538228323</v>
+        <v>1.074910586293353</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.581268361390737</v>
+        <v>4.647269640873049</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682205</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.571585389832049</v>
+        <v>-4.537158460144736</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.170950763973964</v>
+        <v>2.18472153584889</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9649084538228323</v>
+        <v>1.074910586293353</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.578886416514232</v>
+        <v>4.644887695996544</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.6785109377099</v>
+        <v>-4.644084008022587</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.125473783980459</v>
+        <v>2.139244555855385</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8579829059449809</v>
+        <v>0.9679850384155019</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.512024326945156</v>
+        <v>4.578025606427468</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.823529496217149</v>
+        <v>-4.789102566529836</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.068895162720794</v>
+        <v>2.082665934595719</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7129643474377324</v>
+        <v>0.8229664799082533</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.42644199398404</v>
+        <v>4.492443273466353</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.941871262001866</v>
+        <v>-4.740165598717256</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.12148969566466</v>
+        <v>2.202171960978505</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7236503860006225</v>
+        <v>0.90249014391746</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.532784856379528</v>
+        <v>4.64008871112963</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073534</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.993281684322574</v>
+        <v>-4.791576021037963</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.098711223862315</v>
+        <v>2.17939348917616</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7236503860006225</v>
+        <v>0.90249014391746</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.530570553505466</v>
+        <v>4.637874408255569</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720061</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.072701135530326</v>
+        <v>-4.870995472245715</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.066846571453504</v>
+        <v>2.147528836767349</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7236503860006225</v>
+        <v>0.90249014391746</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.530473681579756</v>
+        <v>4.637777536329859</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581134</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.168164133447544</v>
+        <v>-4.966458470162933</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.028655265844661</v>
+        <v>2.109337531158506</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7236503860006225</v>
+        <v>0.90249014391746</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.530467575137799</v>
+        <v>4.637771429887902</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500736</v>
+        <v>3.71539314550073</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.103788222596829</v>
+        <v>-4.902082559312218</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.052502026747557</v>
+        <v>2.133184292061402</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7880262968513376</v>
+        <v>0.9668660547681751</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.56718951821084</v>
+        <v>4.674493372960942</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636271</v>
+        <v>3.736109598636266</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.159157384729022</v>
+        <v>-4.957451721444412</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036088179642407</v>
+        <v>2.116770444956251</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7880262968513376</v>
+        <v>0.9668660547681751</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.572923335958566</v>
+        <v>4.680227190708669</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396014</v>
+        <v>3.736843055396009</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.20459516455985</v>
+        <v>-5.002889501275239</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.017451431053008</v>
+        <v>2.098133696366853</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.745181306173178</v>
+        <v>0.9240210640900155</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.546754704894603</v>
+        <v>4.654058559644706</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396423</v>
+        <v>3.790292685396418</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.116388330412271</v>
+        <v>-4.914682667127661</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.072608557562359</v>
+        <v>2.153290822876204</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.745181306173178</v>
+        <v>0.9240210640900155</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.566629097744922</v>
+        <v>4.673932952495025</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299171</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.010353335206962</v>
+        <v>-4.808647671922351</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.09872325616921</v>
+        <v>2.179405521483055</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.745181306173178</v>
+        <v>0.9240210640900155</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.55032979826965</v>
+        <v>4.657633653019753</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590402</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.827141672073867</v>
+        <v>-4.625436008789256</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.174438870886494</v>
+        <v>2.255121136200339</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.745181306173178</v>
+        <v>0.9240210640900155</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.552760747733696</v>
+        <v>4.660064602483798</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146281</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.755420225060016</v>
+        <v>-4.553714561775405</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.168918635539923</v>
+        <v>2.249600900853769</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8169027531870287</v>
+        <v>0.9957425111038662</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.561584801789895</v>
+        <v>4.668888656539997</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.723809890676843</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.73304719945231</v>
+        <v>-4.531341536167699</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.124783591704178</v>
+        <v>2.205465857018023</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8281585042999302</v>
+        <v>1.006998262216768</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.515253998378808</v>
+        <v>4.62255785312891</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739465</v>
+        <v>3.715627631739459</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.766063495363055</v>
+        <v>-4.564357832078444</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.296775278225236</v>
+        <v>2.37745754353908</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7587211276331787</v>
+        <v>0.9375608855500162</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.658789777264112</v>
+        <v>4.766093632014215</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166406</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.754535859713446</v>
+        <v>-4.552830196428835</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.293307558313328</v>
+        <v>2.373989823627173</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8177217858345411</v>
+        <v>0.9965615437513786</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.686111398013179</v>
+        <v>4.793415252763282</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519026</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.851877361055815</v>
+        <v>-4.650171697771204</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258039070298169</v>
+        <v>2.338721335612014</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7733016036690528</v>
+        <v>0.9521413615858902</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.663127401235674</v>
+        <v>4.770431255985777</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710418</v>
+        <v>3.705221264710413</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.937733390395781</v>
+        <v>-4.73602772711117</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.224947740755021</v>
+        <v>2.305630006068865</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7309255344429177</v>
+        <v>0.9097652923597552</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.638952841892832</v>
+        <v>4.746256696642934</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893111</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.946570187811901</v>
+        <v>-4.74486452452729</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.203832223609075</v>
+        <v>2.28451448892292</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.723483361801567</v>
+        <v>0.9023231197184045</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.616906740128523</v>
+        <v>4.724210594878626</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.715564596950185</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.037952750377359</v>
+        <v>-4.836247087092748</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.177443709627941</v>
+        <v>2.258125974941786</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6321007992361087</v>
+        <v>0.8109405571529462</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.572241713634297</v>
+        <v>4.6795455683844</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171925</v>
+        <v>3.673998560171921</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.026246032390353</v>
+        <v>-4.824540369105742</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.284254654647011</v>
+        <v>2.364936919960856</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6438075172231151</v>
+        <v>0.8226472751399526</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.681394002250769</v>
+        <v>4.788697857000872</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692301</v>
+        <v>3.682496284692296</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.994936606451944</v>
+        <v>-4.72487686502208</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.29981076375378</v>
+        <v>2.407834660325726</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6572989936562493</v>
+        <v>0.8858343583436391</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.692521226842055</v>
+        <v>4.829642445654489</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672915362735307</v>
+        <v>3.672915362735301</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.075157195644985</v>
+        <v>-4.691015059321986</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.480627361354621</v>
+        <v>2.634284215883822</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.6572989936562493</v>
+        <v>0.8858343583436391</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.905426060120113</v>
+        <v>5.042547278932547</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.789144401360273</v>
+        <v>3.715782924255842</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.705832861074768</v>
+        <v>4.618445349779599</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.075157195644985</v>
+        <v>-4.809303368125281</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.480627361354621</v>
+        <v>2.69436757821574</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.6572989936562493</v>
+        <v>0.8858343583436391</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.698896658061136</v>
+        <v>5.149945964785783</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240906.xlsx
+++ b/tame_output/ON/bt/strategyON_20240906.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>150.2%</t>
+          <t>139.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-41.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>423.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-642.5%</t>
+          <t>-656.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-106.8%</t>
+          <t>-123.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.2%</t>
+          <t>587.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-309.4%</t>
+          <t>-307.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-135.4%</t>
+          <t>-145.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>104.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.768371775106606</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.9657582745301734</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.75065808822874</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9735223331986596</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.627183816915722</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>1.01991011294386</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.407163018878712</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.109497469169279</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.274295329815434</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.178538727596413</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.154122246450935</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.227753805382514</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.018868885120958</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.291943252475945</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.078743712478651</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.254030812934294</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-3.958923481567813</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.317248074532837</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-3.961393188029619</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.223904391270557</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.029763374353629</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.115818178226254</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.14163565397978</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.061505975007685</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.197155729872369</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.176328781342852</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.0216814700799</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.251085717251627</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-4.013757095494985</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.2299974958468</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-4.007478892925136</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.161047090276189</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-3.947626273721413</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.195160524389811</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.861382810695035</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.224604180174222</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.906689630094015</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.198257227859156</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-3.935722734796317</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.187195859011337</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.842912253345458</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.153592743483046</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.887301722674885</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.137710431675876</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-4.003843327780228</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.086169498145462</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.0437674223628</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.075691156143101</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.071547820264152</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.076076198751099</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.189928492994291</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8670796496596964</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.298542571437622</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.9437836790015697</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.263133533189479</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9724603204031497</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.224749870631328</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9852332267687789</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
@@ -46516,10 +46516,10 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.047633540596162</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.052808787628147</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.092725785429708</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.035455281456642</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
@@ -46562,10 +46562,10 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.91335036419094</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.100992425258563</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
@@ -46585,10 +46585,10 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-3.958364577711546</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.063794195181911</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.225369087983982</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9626839534118823</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.326566869421154</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.9214087627335146</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.320055902806842</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.9216131109335564</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.301017775099544</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.9257530812247203</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.353533577374365</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>1.024041161948982</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.367400338708283</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>1.019327786401549</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.394721590386775</v>
+        <v>-4.326917346785938</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014407816127078</v>
+        <v>1.041529513567413</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.179174376550935</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>0.9985769229386134</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3599140910246011</v>
@@ -46792,10 +46792,10 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.262995597825634</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.967842055960215</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3599140910246011</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.256842891772849</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.9709654867729871</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.273652189923351</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.9633222442528966</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.211354191147229</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>1.054576997560166</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-4.009563993482071</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.9375850783403565</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.060450706168266</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.987520625588054</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-3.973839963518458</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>1.03679265876402</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.034049261523743</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>1.011244920386578</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-3.984862612839391</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>1.029411197900247</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-3.940489481200823</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>1.047023317991111</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-3.962969832059708</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>1.032424971786148</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-3.915314101498652</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>1.057869021038375</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.814795942999897</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.102968657812601</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.798890613567544</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.096085462061415</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.754052211959146</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.118118525315402</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.773550668201155</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.114480082449677</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.729347831115254</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.138040819811875</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.736907496952301</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.133426953946303</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.578616079413029</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.247991286145052</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.370974075778553</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.329488792193095</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.319941983056025</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.344849857520377</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.254717801928819</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.388126934063964</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.217290781857685</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.399058714391698</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.237402437892393</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.392270844309055</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.20898917479251</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.564193920570219</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.134206913767497</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.714219734198041</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.108122829503689</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.716361343917423</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.020244916394569</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.749705704744851</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.011352455001285</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.770817095028956</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.179828571971163</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.695281695645589</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.733572379341723</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.855053869885227</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.710851275658571</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.854806333855392</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.840053088952613</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.962031734388944</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.865927487426639</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.98875979749298</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.858872797211465</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.988257029568595</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.831921572884977</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>2.009043672943932</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.853465800715764</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.184529113956577</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.875873918520636</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.167682561737621</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-2.904098154098237</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.158446867056218</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-2.913539079986767</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.210924214422653</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.024466795141434</v>
+        <v>-3.002415711155241</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.169444222906087</v>
+        <v>2.178264656500565</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.113167294561979</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.047487742013596</v>
+        <v>4.020035846244808</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.10079677274234</v>
+        <v>-3.078745688756146</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.1370240447595</v>
+        <v>2.145844478353977</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.113167294561979</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.045599554907371</v>
+        <v>4.018147659138584</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.141238229550369</v>
+        <v>-3.172409633433688</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.115667691639151</v>
+        <v>2.103199130085823</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.072725837753949</v>
+        <v>0.9737501902697926</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.016154910425415</v>
+        <v>3.956769521934921</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.302806655077624</v>
+        <v>-3.333978058960943</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.049474331638401</v>
+        <v>2.037005770085074</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9459429139560699</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.93851916635684</v>
+        <v>3.879133777866346</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.411107316947743</v>
+        <v>-3.442278720831062</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.019227473756272</v>
+        <v>2.006758912202944</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9459429139560699</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.951592573222759</v>
+        <v>3.892207184732265</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.428911288668488</v>
+        <v>-3.460082692551806</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.004111081850914</v>
+        <v>1.991642520297587</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8754082910508687</v>
+        <v>0.7764326435667122</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.901276996262578</v>
+        <v>3.841891607772084</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.456812075777961</v>
+        <v>-3.487983479661279</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.991474808134127</v>
+        <v>1.979006246580799</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8408113669079339</v>
+        <v>0.7418357194237774</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.879042882903819</v>
+        <v>3.819657494413325</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.579338178480854</v>
+        <v>-3.610509582364173</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.939228811030168</v>
+        <v>1.926760249476841</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.71828526420504</v>
+        <v>0.6193096167208835</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.802291665259282</v>
+        <v>3.742906276768788</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.809852674666443</v>
+        <v>-3.841024078549762</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.913728972146437</v>
+        <v>1.901260410593109</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4877707680194513</v>
+        <v>0.3887951205352947</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.730688927138432</v>
+        <v>3.671303538647938</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.158597759890887</v>
+        <v>-4.189769163774206</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.914542657058506</v>
+        <v>1.902074095505178</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3790228141005535</v>
+        <v>0.2800471666163969</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.80575187378894</v>
+        <v>3.746366485298446</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.312584177667027</v>
+        <v>-4.343755581550346</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.92192835909369</v>
+        <v>1.909459797540362</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3790228141005535</v>
+        <v>0.2800471666163969</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.87473214293458</v>
+        <v>3.815346754444086</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.262062273839361</v>
+        <v>-4.29323367772268</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.928188322744877</v>
+        <v>1.915719761191549</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3790228141005535</v>
+        <v>0.2800471666163969</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.860783345054701</v>
+        <v>3.801397956564207</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.514537427847086</v>
+        <v>-4.545708831730405</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.839068750197201</v>
+        <v>1.826600188643873</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3790228141005535</v>
+        <v>0.2800471666163969</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.872653834110115</v>
+        <v>3.813268445619621</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.807433184326498</v>
+        <v>-4.838604588209817</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.72312098212438</v>
+        <v>1.710652420571052</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3790228141005535</v>
+        <v>0.2800471666163969</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.873864368629059</v>
+        <v>3.814478980138565</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.994097312461306</v>
+        <v>-5.025268716344625</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.652577073097778</v>
+        <v>1.64010851154445</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3522838432759936</v>
+        <v>0.2533081957918371</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.861942728361644</v>
+        <v>3.802557339871151</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.140117999375268</v>
+        <v>-5.171289403258587</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.589246651068383</v>
+        <v>1.576778089515055</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3432007514821366</v>
+        <v>0.2442251039979801</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.85157072602152</v>
+        <v>3.792185337531026</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.231832008484853</v>
+        <v>-5.263003412368173</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.714765104123593</v>
+        <v>1.702296542570265</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3432007514821366</v>
+        <v>0.2442251039979801</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.013774782720564</v>
+        <v>3.95438939423007</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.263483667544822</v>
+        <v>-5.294655071428142</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.69695107846342</v>
+        <v>1.684482516910091</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3380322942376964</v>
+        <v>0.2390566467535399</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.005520346337714</v>
+        <v>3.94613495784722</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.345418485813705</v>
+        <v>-5.376589889697025</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.674406568724357</v>
+        <v>1.661938007171029</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3280975486506162</v>
+        <v>0.2291219011664597</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.009788916553957</v>
+        <v>3.950403528063463</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.447394608062113</v>
+        <v>-5.478566011945433</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.642541758280897</v>
+        <v>1.630073196727569</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2261214264022087</v>
+        <v>0.1271457789180521</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.957528881660815</v>
+        <v>3.898143493170321</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.337388324584891</v>
+        <v>-5.368559728468211</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.678697158915961</v>
+        <v>1.666228597362633</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2493259983194839</v>
+        <v>0.1503503508353273</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.963604512055355</v>
+        <v>3.904219123564861</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.194328748843965</v>
+        <v>-5.225500152727285</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.740170999934306</v>
+        <v>1.727702438380978</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2573394249094632</v>
+        <v>0.1583637774253066</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.972662578731317</v>
+        <v>3.913277190240823</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.892882023372128</v>
+        <v>-4.924053427255448</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.868010573005576</v>
+        <v>1.855542011452249</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5587861503813004</v>
+        <v>0.4598105028971439</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.160791496896955</v>
+        <v>4.101406108406461</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.917472267607311</v>
+        <v>-4.948643671490632</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.859145653064214</v>
+        <v>1.846677091510885</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5587861503813004</v>
+        <v>0.4598105028971439</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.161762674649666</v>
+        <v>4.102377286159172</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.866433891600791</v>
+        <v>-4.897605295484111</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.880403907846577</v>
+        <v>1.867935346293249</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5587861503813004</v>
+        <v>0.4598105028971439</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.162605579029422</v>
+        <v>4.103220190538927</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.82529459673416</v>
+        <v>-4.85646600061748</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.915897724667375</v>
+        <v>1.903429163114047</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5999254452479312</v>
+        <v>0.5009497977637747</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.206327254823545</v>
+        <v>4.146941866333052</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.72865968471552</v>
+        <v>-4.75983108859884</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.770735685598765</v>
+        <v>1.758267124045438</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6965603572665712</v>
+        <v>0.5975847097824146</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.080492198158664</v>
+        <v>4.02110680966817</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.859240419246363</v>
+        <v>-4.890411823129683</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.722005435860393</v>
+        <v>1.709536874307065</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5659796227357287</v>
+        <v>0.4670039752515721</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.005645801514122</v>
+        <v>3.946260413023628</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833454</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.694744085055401</v>
+        <v>-4.725915488938721</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.77223078861286</v>
+        <v>1.759762227059532</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7304759569266905</v>
+        <v>0.631500309442534</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.088770421104782</v>
+        <v>4.029385032614289</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.617645483513528</v>
+        <v>-4.648816887396849</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.802257939666039</v>
+        <v>1.789789378112711</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7304759569266905</v>
+        <v>0.631500309442534</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.087958131541212</v>
+        <v>4.028572743050718</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.628030678403418</v>
+        <v>-4.659202082286738</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.807972640835156</v>
+        <v>1.795504079281827</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7200907620368012</v>
+        <v>0.6211151145526447</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.091595793732351</v>
+        <v>4.032210405241857</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.646618837125643</v>
+        <v>-4.677790241008963</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.871374383122691</v>
+        <v>1.858905821569363</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7015026033145759</v>
+        <v>0.6025269558304194</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.151279904275441</v>
+        <v>4.091894515784947</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.646917383821679</v>
+        <v>-4.678088787704999</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.868123975262575</v>
+        <v>1.855655413709247</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.70120405661854</v>
+        <v>0.6022284091343835</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.147969787076118</v>
+        <v>4.088584398585624</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.546094250131251</v>
+        <v>-4.577265654014571</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.912984123678137</v>
+        <v>1.900515562124809</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7136682721028939</v>
+        <v>0.6146926246187373</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.159979211306122</v>
+        <v>4.100593822815627</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.355312889378844</v>
+        <v>-4.386484293262164</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.989425921457643</v>
+        <v>1.976957359904315</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9044496328553012</v>
+        <v>0.8054739853711447</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.274577281236109</v>
+        <v>4.215191892745615</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.248349531529422</v>
+        <v>-4.279520935412743</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.012048110335009</v>
+        <v>1.99957954878168</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9629142408151027</v>
+        <v>0.8639385933309461</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.289492891749586</v>
+        <v>4.230107503259092</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.19301894362766</v>
+        <v>-4.22419034751098</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.069147282107772</v>
+        <v>2.056678720554444</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.018244828716865</v>
+        <v>0.9192691812327083</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.357658181102702</v>
+        <v>4.298272792612209</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.180964816714697</v>
+        <v>-4.160501303978051</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.067655500774395</v>
+        <v>2.075840905869053</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.030298955629828</v>
+        <v>0.9829582247656379</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.358577225151918</v>
+        <v>4.330172786633404</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.222119936282918</v>
+        <v>-4.201656423546272</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.053074083131242</v>
+        <v>2.061259488225901</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9891438360616067</v>
+        <v>0.9418031051974169</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.335764783595121</v>
+        <v>4.307360345076607</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.154071373591388</v>
+        <v>-4.133607860854742</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.093144534085737</v>
+        <v>2.101329939180395</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.057192398753136</v>
+        <v>1.009851667888947</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.389444947087921</v>
+        <v>4.361040508569407</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.385671766760889</v>
+        <v>-4.365208254024243</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.02070704699153</v>
+        <v>2.028892452086189</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.057192398753136</v>
+        <v>1.009851667888947</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.409647617261515</v>
+        <v>4.381243178743001</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.4037442750525</v>
+        <v>-4.383280762315854</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.013478043674886</v>
+        <v>2.021663448769544</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.057192398753136</v>
+        <v>1.009851667888947</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.409647617261515</v>
+        <v>4.381243178743001</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.578851107628946</v>
+        <v>-4.558387594892299</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.903687224237774</v>
+        <v>1.911872629332433</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.057192398753136</v>
+        <v>1.009851667888947</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.369899530854982</v>
+        <v>4.341495092336468</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.547565087088491</v>
+        <v>-4.527101574351843</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.923224251450896</v>
+        <v>1.931409656545555</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.088478419293592</v>
+        <v>1.041137688429402</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.395693762176196</v>
+        <v>4.367289323657682</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677826</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.394539694975206</v>
+        <v>-4.374076182238559</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.083605407869115</v>
+        <v>2.091790812963774</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.241503811406876</v>
+        <v>1.194163080542686</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.58667999701707</v>
+        <v>4.558275558498556</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.422847008848477</v>
+        <v>-4.402383496111829</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.259748707228098</v>
+        <v>2.267934112322758</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.241503811406876</v>
+        <v>1.194163080542686</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.774146221925363</v>
+        <v>4.745741783406848</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.589440233961999</v>
+        <v>-4.568976721225352</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.162514368536772</v>
+        <v>2.170699773631431</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.074910586293353</v>
+        <v>1.027569855429163</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.643593238211331</v>
+        <v>4.615188799692817</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.708202704568385</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.566404440600433</v>
+        <v>-4.545940927863786</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.175405088543116</v>
+        <v>2.183590493637775</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.074910586293353</v>
+        <v>1.027569855429163</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.647269640873049</v>
+        <v>4.618865202354534</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682207</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.537158460144736</v>
+        <v>-4.516694947408089</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.18472153584889</v>
+        <v>2.192906940943549</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.074910586293353</v>
+        <v>1.027569855429163</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.644887695996544</v>
+        <v>4.616483257478031</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.69942482753911</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.644084008022587</v>
+        <v>-4.62362049528594</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.139244555855385</v>
+        <v>2.147429960950044</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9679850384155019</v>
+        <v>0.9206443075513121</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.578025606427468</v>
+        <v>4.549621167908954</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.68996278598374</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.789102566529836</v>
+        <v>-4.768639053793189</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.082665934595719</v>
+        <v>2.090851339690378</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8229664799082533</v>
+        <v>0.7756257490440636</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.492443273466353</v>
+        <v>4.464038834947839</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969751</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.740165598717256</v>
+        <v>-4.886980819577906</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.202171960978505</v>
+        <v>2.143445872634244</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.90249014391746</v>
+        <v>0.7863117876069536</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.64008871112963</v>
+        <v>4.570381697343326</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073534</v>
+        <v>3.714899237073541</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.791576021037963</v>
+        <v>-4.938391241898614</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.17939348917616</v>
+        <v>2.1206674008319</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.90249014391746</v>
+        <v>0.7863117876069536</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.637874408255569</v>
+        <v>4.568167394469265</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720061</v>
+        <v>3.704778134720069</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.870995472245715</v>
+        <v>-5.017810693106366</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.147528836767349</v>
+        <v>2.088802748423089</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.90249014391746</v>
+        <v>0.7863117876069536</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.637777536329859</v>
+        <v>4.568070522543555</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581135</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.966458470162933</v>
+        <v>-5.113273691023584</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.109337531158506</v>
+        <v>2.050611442814245</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.90249014391746</v>
+        <v>0.7863117876069536</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.637771429887902</v>
+        <v>4.568064416101598</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.71539314550073</v>
+        <v>3.715393145500737</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.902082559312218</v>
+        <v>-5.048897780172869</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.133184292061402</v>
+        <v>2.074458203717142</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9668660547681751</v>
+        <v>0.8506876984576688</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.674493372960942</v>
+        <v>4.604786359174638</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636266</v>
+        <v>3.736109598636273</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.957451721444412</v>
+        <v>-5.104266942305062</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.116770444956251</v>
+        <v>2.058044356611991</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9668660547681751</v>
+        <v>0.8506876984576688</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.680227190708669</v>
+        <v>4.610520176922365</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396009</v>
+        <v>3.736843055396016</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.002889501275239</v>
+        <v>-5.14970472213589</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.098133696366853</v>
+        <v>2.039407608022593</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9240210640900155</v>
+        <v>0.8078427077795092</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.654058559644706</v>
+        <v>4.584351545858402</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396418</v>
+        <v>3.790292685396424</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.914682667127661</v>
+        <v>-5.061497887988311</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.153290822876204</v>
+        <v>2.094564734531943</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9240210640900155</v>
+        <v>0.8078427077795092</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.673932952495025</v>
+        <v>4.604225938708721</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299171</v>
+        <v>3.794507029299178</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.808647671922351</v>
+        <v>-4.955462892783002</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.179405521483055</v>
+        <v>2.120679433138795</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9240210640900155</v>
+        <v>0.8078427077795092</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.657633653019753</v>
+        <v>4.587926639233449</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590402</v>
+        <v>3.794725278590409</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.625436008789256</v>
+        <v>-4.772251229649907</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.255121136200339</v>
+        <v>2.196395047856078</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9240210640900155</v>
+        <v>0.8078427077795092</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.660064602483798</v>
+        <v>4.590357588697494</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146281</v>
+        <v>3.776866743146288</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.553714561775405</v>
+        <v>-4.700529782636056</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.249600900853769</v>
+        <v>2.190874812509508</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9957425111038662</v>
+        <v>0.8795641547933598</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.668888656539997</v>
+        <v>4.599181642753694</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676843</v>
+        <v>3.72380989067685</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.531341536167699</v>
+        <v>-4.67815675702835</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.205465857018023</v>
+        <v>2.146739768673762</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.006998262216768</v>
+        <v>0.8908199059062614</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.62255785312891</v>
+        <v>4.552850839342606</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739459</v>
+        <v>3.715627631739467</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.564357832078444</v>
+        <v>-4.711173052939094</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.37745754353908</v>
+        <v>2.31873145519482</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9375608855500162</v>
+        <v>0.8213825292395098</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.766093632014215</v>
+        <v>4.696386618227911</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166406</v>
+        <v>3.713782722166414</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.552830196428835</v>
+        <v>-4.699645417289486</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.373989823627173</v>
+        <v>2.315263735282913</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9965615437513786</v>
+        <v>0.8803831874408723</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.793415252763282</v>
+        <v>4.723708238976978</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519026</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.650171697771204</v>
+        <v>-4.796986918631855</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.338721335612014</v>
+        <v>2.279995247267753</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9521413615858902</v>
+        <v>0.8359630052753839</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.770431255985777</v>
+        <v>4.700724242199473</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710413</v>
+        <v>3.705221264710421</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.73602772711117</v>
+        <v>-4.882842947971821</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.305630006068865</v>
+        <v>2.246903917724605</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9097652923597552</v>
+        <v>0.7935869360492489</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.746256696642934</v>
+        <v>4.67654968285663</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893111</v>
+        <v>3.691855684893119</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.74486452452729</v>
+        <v>-4.85708538619141</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.28451448892292</v>
+        <v>2.239626144257271</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9023231197184045</v>
+        <v>0.8058948441393622</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.724210594878626</v>
+        <v>4.6663536295312</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950185</v>
+        <v>3.715564596950192</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.836247087092748</v>
+        <v>-4.948467948756869</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.258125974941786</v>
+        <v>2.213237630276137</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8109405571529462</v>
+        <v>0.714512281573904</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.6795455683844</v>
+        <v>4.621688603036975</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171921</v>
+        <v>3.673998560171927</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.824540369105742</v>
+        <v>-4.936761230769863</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.364936919960856</v>
+        <v>2.320048575295208</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8226472751399526</v>
+        <v>0.7262189995609104</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.788697857000872</v>
+        <v>4.730840891653447</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692296</v>
+        <v>3.682496284692304</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.72487686502208</v>
+        <v>-4.8370977266862</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.407834660325726</v>
+        <v>2.362946315660078</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8858343583436391</v>
+        <v>0.7894060827645969</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.829642445654489</v>
+        <v>4.771785480307063</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672915362735301</v>
+        <v>3.672915362735308</v>
       </c>
       <c r="C2078" t="n">
         <v>4.511046663926363</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.691015059321986</v>
+        <v>-4.847413824852552</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.634284215883822</v>
+        <v>2.571724709671595</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8858343583436391</v>
+        <v>0.7894060827645969</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.042547278932547</v>
+        <v>4.984690313585121</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.715782924255842</v>
+        <v>3.789144401360275</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.618445349779599</v>
+        <v>4.510225330838453</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.809303368125281</v>
+        <v>-4.952923304417289</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.69436757821574</v>
+        <v>2.52869958475779</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8858343583436391</v>
+        <v>0.7894060827645969</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.149945964785783</v>
+        <v>4.983868980497212</v>
       </c>
     </row>
   </sheetData>
